--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1880,20 +1880,20 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v/>
+        <v>0.012</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v/>
+        <v>0.008</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v/>
+        <v>0.129</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v/>
+        <v>0.129</v>
       </c>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
@@ -1908,331 +1908,6 @@
       <c r="R28" s="7" t="n"/>
       <c r="S28" s="7" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>ordered</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="7" t="n"/>
-      <c r="Q29" s="7" t="n"/>
-      <c r="R29" s="7" t="n"/>
-      <c r="S29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
-      <c r="P30" s="7" t="n"/>
-      <c r="Q30" s="7" t="n"/>
-      <c r="R30" s="7" t="n"/>
-      <c r="S30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P31" s="7" t="n"/>
-      <c r="Q31" s="7" t="n"/>
-      <c r="R31" s="7" t="n"/>
-      <c r="S31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
-      <c r="K32" s="7" t="n"/>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="7" t="n"/>
-      <c r="P32" s="7" t="n"/>
-      <c r="Q32" s="7" t="n"/>
-      <c r="R32" s="7" t="n"/>
-      <c r="S32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>abde</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="7" t="n"/>
-      <c r="Q33" s="7" t="n"/>
-      <c r="R33" s="7" t="n"/>
-      <c r="S33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="6" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="O34" s="6" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="P34" s="7" t="n"/>
-      <c r="Q34" s="7" t="n"/>
-      <c r="R34" s="7" t="n"/>
-      <c r="S34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
-      <c r="P35" s="6" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="S35" s="6" t="n">
-        <v>0.172</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>abde</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
-      <c r="P36" s="6" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="S36" s="6" t="n">
-        <v>0.172</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
-      <c r="P37" s="6" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="S37" s="6" t="n">
-        <v>0.172</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="H1:K1"/>
@@ -2244,7 +1919,7 @@
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D37">
+  <conditionalFormatting sqref="D4:D28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2256,7 +1931,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E37">
+  <conditionalFormatting sqref="E4:E28">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2268,7 +1943,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F37">
+  <conditionalFormatting sqref="F4:F28">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2280,7 +1955,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G37">
+  <conditionalFormatting sqref="G4:G28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2292,7 +1967,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H37">
+  <conditionalFormatting sqref="H4:H28">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2304,7 +1979,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I37">
+  <conditionalFormatting sqref="I4:I28">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2316,7 +1991,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J37">
+  <conditionalFormatting sqref="J4:J28">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2328,7 +2003,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K37">
+  <conditionalFormatting sqref="K4:K28">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2340,7 +2015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L37">
+  <conditionalFormatting sqref="L4:L28">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2352,7 +2027,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M37">
+  <conditionalFormatting sqref="M4:M28">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2364,7 +2039,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N37">
+  <conditionalFormatting sqref="N4:N28">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2376,7 +2051,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O37">
+  <conditionalFormatting sqref="O4:O28">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2388,7 +2063,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P37">
+  <conditionalFormatting sqref="P4:P28">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2400,7 +2075,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q37">
+  <conditionalFormatting sqref="Q4:Q28">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2412,7 +2087,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R37">
+  <conditionalFormatting sqref="R4:R28">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2424,7 +2099,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S37">
+  <conditionalFormatting sqref="S4:S28">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1899,14 +1899,104 @@
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="7" t="n"/>
+      <c r="L28" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>0.244</v>
+      </c>
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="7" t="n"/>
       <c r="R28" s="7" t="n"/>
       <c r="S28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P29" s="7" t="n"/>
+      <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="7" t="n"/>
+      <c r="S29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="P30" s="7" t="n"/>
+      <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="7" t="n"/>
+      <c r="S30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1919,7 +2009,7 @@
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D28">
+  <conditionalFormatting sqref="D4:D30">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1931,7 +2021,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E28">
+  <conditionalFormatting sqref="E4:E30">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1943,7 +2033,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F28">
+  <conditionalFormatting sqref="F4:F30">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1955,7 +2045,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G28">
+  <conditionalFormatting sqref="G4:G30">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1967,7 +2057,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H28">
+  <conditionalFormatting sqref="H4:H30">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1979,7 +2069,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I28">
+  <conditionalFormatting sqref="I4:I30">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1991,7 +2081,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J28">
+  <conditionalFormatting sqref="J4:J30">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2003,7 +2093,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K28">
+  <conditionalFormatting sqref="K4:K30">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2015,7 +2105,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L28">
+  <conditionalFormatting sqref="L4:L30">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2027,7 +2117,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M28">
+  <conditionalFormatting sqref="M4:M30">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2039,7 +2129,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N28">
+  <conditionalFormatting sqref="N4:N30">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2051,7 +2141,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O28">
+  <conditionalFormatting sqref="O4:O30">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2063,7 +2153,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P28">
+  <conditionalFormatting sqref="P4:P30">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2075,7 +2165,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q28">
+  <conditionalFormatting sqref="Q4:Q30">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2087,7 +2177,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R28">
+  <conditionalFormatting sqref="R4:R30">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2099,7 +2189,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S28">
+  <conditionalFormatting sqref="S4:S30">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Master Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Comparison" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -952,7 +952,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0A</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -965,53 +965,37 @@
           <t>ade</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.161</v>
-      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="6" t="n">
-        <v>0.104</v>
+        <v>0.04</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.077</v>
+        <v>0.028</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.435</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>0.17</v>
-      </c>
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="O10" s="7" t="n"/>
       <c r="P10" s="6" t="n">
-        <v>0.177</v>
+        <v>0.134</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0.177</v>
+        <v>0.143</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>0.441</v>
+        <v>0.596</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0.251</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="11">
@@ -1022,53 +1006,37 @@
           <t>abde</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.151</v>
-      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
       <c r="H11" s="6" t="n">
-        <v>0.119</v>
+        <v>0.055</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.094</v>
+        <v>0.047</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.383</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="O11" s="6" t="n">
-        <v>0.162</v>
-      </c>
+        <v>0.437</v>
+      </c>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
       <c r="P11" s="6" t="n">
-        <v>0.23</v>
+        <v>0.274</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>0.249</v>
+        <v>0.377</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0.447</v>
+        <v>0.556</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.254</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="12">
@@ -1079,53 +1047,37 @@
           <t>abcde</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0.151</v>
-      </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="n">
-        <v>0.119</v>
+        <v>0.055</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.094</v>
+        <v>0.047</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.383</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="O12" s="6" t="n">
-        <v>0.162</v>
-      </c>
+        <v>0.437</v>
+      </c>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+      <c r="O12" s="7" t="n"/>
       <c r="P12" s="6" t="n">
-        <v>0.23</v>
+        <v>0.274</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>0.249</v>
+        <v>0.377</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0.447</v>
+        <v>0.556</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.254</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="13">
@@ -1145,32 +1097,32 @@
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="6" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.293</v>
+        <v>0.367</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.265</v>
+        <v>0.19</v>
       </c>
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="7" t="n"/>
       <c r="P13" s="6" t="n">
-        <v>0.224</v>
+        <v>0.31</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0.226</v>
+        <v>0.364</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0.419</v>
+        <v>0.435</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0.301</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="14">
@@ -1186,32 +1138,32 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="6" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.092</v>
+        <v>0.13</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.252</v>
+        <v>0.297</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.17</v>
+        <v>0.166</v>
       </c>
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="6" t="n">
-        <v>0.227</v>
+        <v>0.319</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>0.231</v>
+        <v>0.374</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>0.421</v>
+        <v>0.429</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.302</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="15">
@@ -1227,38 +1179,38 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="6" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.092</v>
+        <v>0.13</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.252</v>
+        <v>0.297</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.17</v>
+        <v>0.166</v>
       </c>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="7" t="n"/>
       <c r="P15" s="6" t="n">
-        <v>0.227</v>
+        <v>0.319</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.231</v>
+        <v>0.374</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>0.421</v>
+        <v>0.429</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.302</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1272,52 +1224,52 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.179</v>
+        <v>0.196</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.132</v>
+        <v>0.161</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.098</v>
+        <v>0.104</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.355</v>
+        <v>0.435</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.309</v>
+        <v>0.354</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.059</v>
+        <v>0.036</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.054</v>
+        <v>0.029</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.388</v>
+        <v>0.258</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.209</v>
+        <v>0.177</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0.206</v>
+        <v>0.177</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.403</v>
+        <v>0.441</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.241</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="17">
@@ -1329,52 +1281,52 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.189</v>
+        <v>0.207</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.336</v>
+        <v>0.383</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.231</v>
+        <v>0.271</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.062</v>
+        <v>0.037</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.057</v>
+        <v>0.031</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.396</v>
+        <v>0.253</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.282</v>
+        <v>0.162</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.209</v>
+        <v>0.23</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.206</v>
+        <v>0.249</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.403</v>
+        <v>0.447</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="18">
@@ -1386,52 +1338,52 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.189</v>
+        <v>0.207</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.336</v>
+        <v>0.383</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.231</v>
+        <v>0.271</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.062</v>
+        <v>0.037</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.057</v>
+        <v>0.031</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.396</v>
+        <v>0.253</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.282</v>
+        <v>0.162</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.209</v>
+        <v>0.23</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>0.206</v>
+        <v>0.249</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>0.403</v>
+        <v>0.447</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="19">
@@ -1451,32 +1403,32 @@
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="6" t="n">
-        <v>0.037</v>
+        <v>0.111</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.029</v>
+        <v>0.081</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.543</v>
+        <v>0.293</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.438</v>
+        <v>0.265</v>
       </c>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
       <c r="O19" s="7" t="n"/>
       <c r="P19" s="6" t="n">
-        <v>0.28</v>
+        <v>0.224</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.265</v>
+        <v>0.226</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.387</v>
+        <v>0.419</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.278</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="20">
@@ -1492,32 +1444,32 @@
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="6" t="n">
-        <v>0.039</v>
+        <v>0.119</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.03</v>
+        <v>0.092</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.491</v>
+        <v>0.252</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.319</v>
+        <v>0.17</v>
       </c>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="7" t="n"/>
       <c r="P20" s="6" t="n">
-        <v>0.28</v>
+        <v>0.227</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0.265</v>
+        <v>0.231</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>0.387</v>
+        <v>0.421</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0.278</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="21">
@@ -1533,38 +1485,38 @@
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="6" t="n">
-        <v>0.039</v>
+        <v>0.119</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.03</v>
+        <v>0.092</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.491</v>
+        <v>0.252</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.319</v>
+        <v>0.17</v>
       </c>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
       <c r="O21" s="7" t="n"/>
       <c r="P21" s="6" t="n">
-        <v>0.28</v>
+        <v>0.227</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>0.265</v>
+        <v>0.231</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>0.387</v>
+        <v>0.421</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.278</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1578,52 +1530,52 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.113</v>
+        <v>0.179</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.04</v>
+        <v>0.098</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.039</v>
+        <v>0.076</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.628</v>
+        <v>0.355</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.303</v>
+        <v>0.309</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.294</v>
+        <v>0.388</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.122</v>
+        <v>0.209</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0.12</v>
+        <v>0.206</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>0.547</v>
+        <v>0.403</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.275</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="23">
@@ -1635,52 +1587,52 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.112</v>
+        <v>0.189</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.058</v>
+        <v>0.11</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.066</v>
+        <v>0.09</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.161</v>
+        <v>0.231</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.293</v>
+        <v>0.396</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.172</v>
+        <v>0.282</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.334</v>
+        <v>0.209</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.409</v>
+        <v>0.206</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0.509</v>
+        <v>0.403</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.181</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="24">
@@ -1692,52 +1644,52 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.112</v>
+        <v>0.189</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.058</v>
+        <v>0.11</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.066</v>
+        <v>0.09</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.161</v>
+        <v>0.231</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.293</v>
+        <v>0.396</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.172</v>
+        <v>0.282</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.334</v>
+        <v>0.209</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>0.409</v>
+        <v>0.206</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>0.509</v>
+        <v>0.403</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.181</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="25">
@@ -1757,32 +1709,32 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.055</v>
+        <v>0.029</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.5</v>
+        <v>0.543</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.157</v>
+        <v>0.438</v>
       </c>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="7" t="n"/>
       <c r="P25" s="6" t="n">
-        <v>0.319</v>
+        <v>0.28</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.309</v>
+        <v>0.265</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>0.439</v>
+        <v>0.387</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.269</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="26">
@@ -1798,32 +1750,32 @@
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="6" t="n">
-        <v>0.077</v>
+        <v>0.039</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.099</v>
+        <v>0.03</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.52</v>
+        <v>0.491</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.182</v>
+        <v>0.319</v>
       </c>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="7" t="n"/>
       <c r="P26" s="6" t="n">
-        <v>0.358</v>
+        <v>0.28</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0.359</v>
+        <v>0.265</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>0.409</v>
+        <v>0.387</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.234</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="27">
@@ -1839,38 +1791,38 @@
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="6" t="n">
-        <v>0.077</v>
+        <v>0.039</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.099</v>
+        <v>0.03</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.52</v>
+        <v>0.491</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.182</v>
+        <v>0.319</v>
       </c>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="7" t="n"/>
       <c r="P27" s="6" t="n">
-        <v>0.358</v>
+        <v>0.28</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.359</v>
+        <v>0.265</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>0.409</v>
+        <v>0.387</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.234</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1884,37 +1836,53 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.012</v>
+        <v>0.036</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.129</v>
+        <v>0.113</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>0.303</v>
+      </c>
       <c r="L28" s="6" t="n">
-        <v>0.031</v>
+        <v>0.052</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.022</v>
+        <v>0.05</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.309</v>
+        <v>0.294</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="P28" s="7" t="n"/>
-      <c r="Q28" s="7" t="n"/>
-      <c r="R28" s="7" t="n"/>
-      <c r="S28" s="7" t="n"/>
+        <v>0.17</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>0.275</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1925,37 +1893,53 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.012</v>
+        <v>0.036</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.129</v>
+        <v>0.112</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>0.161</v>
+      </c>
       <c r="L29" s="6" t="n">
-        <v>0.031</v>
+        <v>0.053</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.022</v>
+        <v>0.052</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.309</v>
+        <v>0.293</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="P29" s="7" t="n"/>
-      <c r="Q29" s="7" t="n"/>
-      <c r="R29" s="7" t="n"/>
-      <c r="S29" s="7" t="n"/>
+        <v>0.172</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>0.181</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1966,37 +1950,564 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>0.181</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+      <c r="O31" s="7" t="n"/>
+      <c r="P31" s="6" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>0.269</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
+      <c r="O32" s="7" t="n"/>
+      <c r="P32" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>0.234</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="7" t="n"/>
+      <c r="P33" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>0.234</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
         <v>0.012</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>0.008</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F37" s="6" t="n">
         <v>0.129</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G37" s="6" t="n">
         <v>0.129</v>
       </c>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="6" t="n">
+      <c r="H37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L37" s="6" t="n">
         <v>0.031</v>
       </c>
-      <c r="M30" s="6" t="n">
+      <c r="M37" s="6" t="n">
         <v>0.022</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N37" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="7" t="n"/>
+      <c r="O38" s="7" t="n"/>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="7" t="n"/>
+      <c r="O40" s="7" t="n"/>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N41" s="6" t="n">
         <v>0.304</v>
       </c>
-      <c r="O30" s="6" t="n">
+      <c r="O41" s="6" t="n">
         <v>0.241</v>
       </c>
-      <c r="P30" s="7" t="n"/>
-      <c r="Q30" s="7" t="n"/>
-      <c r="R30" s="7" t="n"/>
-      <c r="S30" s="7" t="n"/>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2009,7 +2520,7 @@
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D30">
+  <conditionalFormatting sqref="D4:D41">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2021,7 +2532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E30">
+  <conditionalFormatting sqref="E4:E41">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2033,7 +2544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F30">
+  <conditionalFormatting sqref="F4:F41">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2045,7 +2556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G30">
+  <conditionalFormatting sqref="G4:G41">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2057,7 +2568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H30">
+  <conditionalFormatting sqref="H4:H41">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2069,7 +2580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I30">
+  <conditionalFormatting sqref="I4:I41">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2081,7 +2592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J30">
+  <conditionalFormatting sqref="J4:J41">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2093,7 +2604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K30">
+  <conditionalFormatting sqref="K4:K41">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2105,7 +2616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L30">
+  <conditionalFormatting sqref="L4:L41">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2117,7 +2628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M30">
+  <conditionalFormatting sqref="M4:M41">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2129,7 +2640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N30">
+  <conditionalFormatting sqref="N4:N41">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2141,7 +2652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O30">
+  <conditionalFormatting sqref="O4:O41">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2153,7 +2664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P30">
+  <conditionalFormatting sqref="P4:P41">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2165,7 +2676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q30">
+  <conditionalFormatting sqref="Q4:Q41">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2177,7 +2688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R30">
+  <conditionalFormatting sqref="R4:R41">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2189,7 +2700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S30">
+  <conditionalFormatting sqref="S4:S41">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
@@ -839,40 +839,32 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="n">
-        <v>0.248</v>
+        <v/>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.493</v>
+        <v/>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.742</v>
+        <v/>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.09</v>
+        <v/>
       </c>
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
       <c r="O7" s="7" t="n"/>
-      <c r="P7" s="6" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>0.122</v>
-      </c>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
@@ -880,40 +872,32 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="6" t="n">
-        <v>0.248</v>
+        <v/>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.493</v>
+        <v/>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.742</v>
+        <v/>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.09</v>
+        <v/>
       </c>
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="7" t="n"/>
-      <c r="P8" s="6" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="S8" s="6" t="n">
-        <v>0.122</v>
-      </c>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
@@ -921,81 +905,81 @@
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="6" t="n">
-        <v>0.248</v>
+        <v/>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.493</v>
+        <v/>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.742</v>
+        <v/>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.09</v>
+        <v/>
       </c>
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
       <c r="O9" s="7" t="n"/>
-      <c r="P9" s="6" t="n">
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="P10" s="6" t="n">
         <v>0.407</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.751</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>0.761</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="S10" s="6" t="n">
         <v>0.122</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>P0A</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="6" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>0.213</v>
       </c>
     </row>
     <row r="11">
@@ -1003,7 +987,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="D11" s="7" t="n"/>
@@ -1011,85 +995,89 @@
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="6" t="n">
-        <v>0.055</v>
+        <v/>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.047</v>
+        <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v/>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.437</v>
+        <v/>
       </c>
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
       <c r="N11" s="7" t="n"/>
       <c r="O11" s="7" t="n"/>
-      <c r="P11" s="6" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>0.188</v>
-      </c>
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
       <c r="H12" s="6" t="n">
-        <v>0.055</v>
+        <v/>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.047</v>
+        <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.5610000000000001</v>
+        <v/>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
+        <v/>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
       <c r="P12" s="6" t="n">
-        <v>0.274</v>
+        <v>0.407</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>0.377</v>
+        <v>0.751</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0.556</v>
+        <v>0.761</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.188</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>abc</t>
         </is>
       </c>
       <c r="D13" s="7" t="n"/>
@@ -1097,81 +1085,97 @@
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="6" t="n">
-        <v>0.091</v>
+        <v/>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.083</v>
+        <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.367</v>
+        <v/>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.19</v>
+        <v/>
       </c>
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="7" t="n"/>
-      <c r="P13" s="6" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0.238</v>
-      </c>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
       <c r="H14" s="6" t="n">
-        <v>0.12</v>
+        <v/>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.13</v>
+        <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.297</v>
+        <v/>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
+        <v/>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
       <c r="P14" s="6" t="n">
-        <v>0.319</v>
+        <v>0.407</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>0.374</v>
+        <v>0.751</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>0.429</v>
+        <v>0.761</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.234</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>P0A</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D15" s="7" t="n"/>
@@ -1179,97 +1183,89 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="6" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I15" s="6" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0.213</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="M16" s="6" t="n">
         <v>0.13</v>
       </c>
-      <c r="J15" s="6" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="6" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0.234</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>0.029</v>
-      </c>
       <c r="N16" s="6" t="n">
-        <v>0.258</v>
+        <v>0.333</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.17</v>
+        <v>0.118</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.177</v>
+        <v>0.274</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0.177</v>
+        <v>0.377</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0.441</v>
+        <v>0.556</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.251</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="17">
@@ -1277,158 +1273,166 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0.151</v>
-      </c>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
       <c r="H17" s="6" t="n">
-        <v>0.119</v>
+        <v>0.055</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.094</v>
+        <v>0.047</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.383</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.271</v>
+        <v>0.437</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.037</v>
+        <v>0.129</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.031</v>
+        <v>0.13</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.253</v>
+        <v>0.333</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.162</v>
+        <v>0.118</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.23</v>
+        <v>0.274</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.249</v>
+        <v>0.377</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.447</v>
+        <v>0.556</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.254</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.045</v>
+        <v>0.034</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.207</v>
+        <v>0.235</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.151</v>
+        <v>0.101</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.119</v>
+        <v>0.091</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.383</v>
+        <v>0.367</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.271</v>
+        <v>0.19</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.037</v>
+        <v>0.209</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.031</v>
+        <v>0.215</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.253</v>
+        <v>0.29</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.162</v>
+        <v>0.144</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>0.249</v>
+        <v>0.364</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>0.447</v>
+        <v>0.435</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.254</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.103</v>
+      </c>
       <c r="H19" s="6" t="n">
-        <v>0.111</v>
+        <v>0.12</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.081</v>
+        <v>0.13</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.293</v>
+        <v>0.297</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="7" t="n"/>
+        <v>0.166</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>0.144</v>
+      </c>
       <c r="P19" s="6" t="n">
-        <v>0.224</v>
+        <v>0.319</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.226</v>
+        <v>0.374</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.419</v>
+        <v>0.429</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.301</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="20">
@@ -1436,146 +1440,178 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="inlineStr">
         <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0.234</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
           <t>abde</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="n">
+      <c r="D22" s="6" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="H22" s="6" t="n">
         <v>0.119</v>
       </c>
-      <c r="I20" s="6" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="6" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0.302</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="6" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0.302</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
+      <c r="I22" s="6" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="L22" s="6" t="n">
         <v>0.037</v>
       </c>
-      <c r="E22" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>0.059</v>
-      </c>
       <c r="M22" s="6" t="n">
-        <v>0.054</v>
+        <v>0.031</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.388</v>
+        <v>0.253</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.28</v>
+        <v>0.162</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.209</v>
+        <v>0.23</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0.206</v>
+        <v>0.249</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>0.403</v>
+        <v>0.447</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="23">
@@ -1583,158 +1619,174 @@
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.189</v>
+        <v>0.207</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.336</v>
+        <v>0.383</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.231</v>
+        <v>0.271</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.062</v>
+        <v>0.037</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.057</v>
+        <v>0.031</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.396</v>
+        <v>0.253</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.282</v>
+        <v>0.162</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.209</v>
+        <v>0.23</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.206</v>
+        <v>0.249</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0.403</v>
+        <v>0.447</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="F24" s="6" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="O24" s="6" t="n">
         <v>0.189</v>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>0.282</v>
-      </c>
       <c r="P24" s="6" t="n">
-        <v>0.209</v>
+        <v>0.224</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>0.206</v>
+        <v>0.226</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>0.403</v>
+        <v>0.419</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.241</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
+      <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.183</v>
+      </c>
       <c r="H25" s="6" t="n">
-        <v>0.037</v>
+        <v>0.119</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.029</v>
+        <v>0.092</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.543</v>
+        <v>0.252</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
+        <v>0.17</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>0.181</v>
+      </c>
       <c r="P25" s="6" t="n">
-        <v>0.28</v>
+        <v>0.227</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.265</v>
+        <v>0.231</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>0.387</v>
+        <v>0.421</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.278</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="26">
@@ -1742,146 +1794,178 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>0.302</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="S27" s="6" t="n">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
           <t>abde</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="6" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n"/>
-      <c r="O26" s="7" t="n"/>
-      <c r="P26" s="6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>0.278</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="6" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
-      <c r="P27" s="6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="S27" s="6" t="n">
-        <v>0.278</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
       <c r="D28" s="6" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.113</v>
+        <v>0.189</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.039</v>
+        <v>0.09</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.628</v>
+        <v>0.336</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.303</v>
+        <v>0.231</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.052</v>
+        <v>0.062</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.05</v>
+        <v>0.057</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.294</v>
+        <v>0.396</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.17</v>
+        <v>0.282</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.122</v>
+        <v>0.209</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0.12</v>
+        <v>0.206</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>0.547</v>
+        <v>0.403</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.275</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="29">
@@ -1889,158 +1973,174 @@
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.112</v>
+        <v>0.189</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.058</v>
+        <v>0.11</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.066</v>
+        <v>0.09</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.161</v>
+        <v>0.231</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.293</v>
+        <v>0.396</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.172</v>
+        <v>0.282</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.334</v>
+        <v>0.209</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.409</v>
+        <v>0.206</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>0.509</v>
+        <v>0.403</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.181</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.036</v>
+        <v>0.098</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.038</v>
+        <v>0.115</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.112</v>
+        <v>0.304</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.058</v>
+        <v>0.037</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.066</v>
+        <v>0.029</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.543</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.161</v>
+        <v>0.438</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.053</v>
+        <v>0.125</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.052</v>
+        <v>0.15</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.293</v>
+        <v>0.422</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.172</v>
+        <v>0.187</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.334</v>
+        <v>0.28</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0.409</v>
+        <v>0.265</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>0.509</v>
+        <v>0.387</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.181</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
+      <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.16</v>
+      </c>
       <c r="H31" s="6" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.055</v>
+        <v>0.03</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
+        <v>0.319</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>0.186</v>
+      </c>
       <c r="P31" s="6" t="n">
-        <v>0.319</v>
+        <v>0.28</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0.309</v>
+        <v>0.265</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>0.439</v>
+        <v>0.387</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.269</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="32">
@@ -2048,130 +2148,178 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>0.278</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
           <t>abde</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="6" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="7" t="n"/>
-      <c r="P32" s="6" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="R32" s="6" t="n">
+      <c r="D34" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="Q34" s="6" t="n">
         <v>0.409</v>
       </c>
-      <c r="S32" s="6" t="n">
-        <v>0.234</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="6" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="7" t="n"/>
-      <c r="P33" s="6" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="S33" s="6" t="n">
-        <v>0.234</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
       <c r="R34" s="6" t="n">
-        <v/>
+        <v>0.509</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v/>
+        <v>0.181</v>
       </c>
     </row>
     <row r="35">
@@ -2179,48 +2327,68 @@
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ordered</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
       <c r="H35" s="6" t="n">
-        <v/>
+        <v>0.058</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v/>
+        <v>0.066</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v/>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
+        <v>0.161</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>0.172</v>
+      </c>
       <c r="P35" s="6" t="n">
-        <v/>
+        <v>0.334</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v/>
+        <v>0.409</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v/>
+        <v>0.509</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v/>
+        <v>0.181</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D36" s="7" t="n"/>
@@ -2243,39 +2411,23 @@
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="7" t="n"/>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="6" t="n">
-        <v/>
-      </c>
+      <c r="P36" s="7" t="n"/>
+      <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="7" t="n"/>
+      <c r="S36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>0.129</v>
-      </c>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
       <c r="H37" s="6" t="n">
         <v/>
       </c>
@@ -2288,37 +2440,21 @@
       <c r="K37" s="6" t="n">
         <v/>
       </c>
-      <c r="L37" s="6" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="M37" s="6" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="N37" s="6" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="O37" s="6" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="6" t="n">
-        <v/>
-      </c>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+      <c r="P37" s="7" t="n"/>
+      <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="7" t="n"/>
+      <c r="S37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D38" s="7" t="n"/>
@@ -2341,38 +2477,30 @@
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="n"/>
       <c r="O38" s="7" t="n"/>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="6" t="n">
-        <v/>
-      </c>
+      <c r="P38" s="7" t="n"/>
+      <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="7" t="n"/>
+      <c r="S38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.012</v>
+        <v>0.128</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.008</v>
+        <v>0.145</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.129</v>
+        <v>0.333</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.129</v>
+        <v>0.212</v>
       </c>
       <c r="H39" s="6" t="n">
         <v/>
@@ -2387,28 +2515,28 @@
         <v/>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.031</v>
+        <v>0.228</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.022</v>
+        <v>0.233</v>
       </c>
       <c r="N39" s="6" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="Q39" s="6" t="n">
         <v>0.309</v>
       </c>
-      <c r="O39" s="6" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
       <c r="R39" s="6" t="n">
-        <v/>
+        <v>0.439</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v/>
+        <v>0.269</v>
       </c>
     </row>
     <row r="40">
@@ -2416,7 +2544,7 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="D40" s="7" t="n"/>
@@ -2439,75 +2567,776 @@
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="n"/>
       <c r="O40" s="7" t="n"/>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v/>
-      </c>
+      <c r="P40" s="7" t="n"/>
+      <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="7" t="n"/>
+      <c r="S40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0.234</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="7" t="n"/>
+      <c r="O42" s="7" t="n"/>
+      <c r="P42" s="7" t="n"/>
+      <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="7" t="n"/>
+      <c r="S42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
           <t>abcde</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D43" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="S43" s="6" t="n">
+        <v>0.234</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
         <v>0.012</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E47" s="6" t="n">
         <v>0.008</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F47" s="6" t="n">
         <v>0.129</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G47" s="6" t="n">
         <v>0.129</v>
       </c>
-      <c r="H41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="6" t="n">
+      <c r="H47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L47" s="6" t="n">
         <v>0.031</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="M47" s="6" t="n">
         <v>0.022</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N47" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
+      <c r="N48" s="7" t="n"/>
+      <c r="O48" s="7" t="n"/>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
+      <c r="O50" s="7" t="n"/>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N51" s="6" t="n">
         <v>0.304</v>
       </c>
-      <c r="O41" s="6" t="n">
+      <c r="O51" s="6" t="n">
         <v>0.241</v>
       </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="6" t="n">
-        <v/>
-      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="7" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P52" s="7" t="n"/>
+      <c r="Q52" s="7" t="n"/>
+      <c r="R52" s="7" t="n"/>
+      <c r="S52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="7" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P53" s="7" t="n"/>
+      <c r="Q53" s="7" t="n"/>
+      <c r="R53" s="7" t="n"/>
+      <c r="S53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+      <c r="J54" s="7" t="n"/>
+      <c r="K54" s="7" t="n"/>
+      <c r="L54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P54" s="7" t="n"/>
+      <c r="Q54" s="7" t="n"/>
+      <c r="R54" s="7" t="n"/>
+      <c r="S54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+      <c r="J55" s="7" t="n"/>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P55" s="7" t="n"/>
+      <c r="Q55" s="7" t="n"/>
+      <c r="R55" s="7" t="n"/>
+      <c r="S55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+      <c r="J56" s="7" t="n"/>
+      <c r="K56" s="7" t="n"/>
+      <c r="L56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P56" s="7" t="n"/>
+      <c r="Q56" s="7" t="n"/>
+      <c r="R56" s="7" t="n"/>
+      <c r="S56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+      <c r="J57" s="7" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P57" s="7" t="n"/>
+      <c r="Q57" s="7" t="n"/>
+      <c r="R57" s="7" t="n"/>
+      <c r="S57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P58" s="7" t="n"/>
+      <c r="Q58" s="7" t="n"/>
+      <c r="R58" s="7" t="n"/>
+      <c r="S58" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2520,7 +3349,7 @@
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D41">
+  <conditionalFormatting sqref="D4:D58">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2532,7 +3361,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E41">
+  <conditionalFormatting sqref="E4:E58">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2544,7 +3373,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F41">
+  <conditionalFormatting sqref="F4:F58">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2556,7 +3385,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G41">
+  <conditionalFormatting sqref="G4:G58">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2568,7 +3397,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H41">
+  <conditionalFormatting sqref="H4:H58">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2580,7 +3409,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I41">
+  <conditionalFormatting sqref="I4:I58">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2592,7 +3421,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J41">
+  <conditionalFormatting sqref="J4:J58">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2604,7 +3433,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K41">
+  <conditionalFormatting sqref="K4:K58">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2616,7 +3445,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L41">
+  <conditionalFormatting sqref="L4:L58">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2628,7 +3457,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M41">
+  <conditionalFormatting sqref="M4:M58">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2640,7 +3469,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N41">
+  <conditionalFormatting sqref="N4:N58">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2652,7 +3481,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O41">
+  <conditionalFormatting sqref="O4:O58">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2664,7 +3493,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P41">
+  <conditionalFormatting sqref="P4:P58">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2676,7 +3505,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q41">
+  <conditionalFormatting sqref="Q4:Q58">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2688,7 +3517,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R41">
+  <conditionalFormatting sqref="R4:R58">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2700,7 +3529,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S41">
+  <conditionalFormatting sqref="S4:S58">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -2838,7 +2838,7 @@
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D43">
+  <conditionalFormatting sqref="D4:D9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2850,7 +2850,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E43">
+  <conditionalFormatting sqref="E4:E9">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2862,7 +2862,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F43">
+  <conditionalFormatting sqref="F4:F9">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2874,7 +2874,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G43">
+  <conditionalFormatting sqref="G4:G9">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2886,7 +2886,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H43">
+  <conditionalFormatting sqref="H4:H9">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2898,7 +2898,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I43">
+  <conditionalFormatting sqref="I4:I9">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2910,7 +2910,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J43">
+  <conditionalFormatting sqref="J4:J9">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2922,7 +2922,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K43">
+  <conditionalFormatting sqref="K4:K9">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2934,7 +2934,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L43">
+  <conditionalFormatting sqref="L4:L9">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2946,7 +2946,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M43">
+  <conditionalFormatting sqref="M4:M9">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2958,7 +2958,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N43">
+  <conditionalFormatting sqref="N4:N9">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2970,7 +2970,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O43">
+  <conditionalFormatting sqref="O4:O9">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2982,7 +2982,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P43">
+  <conditionalFormatting sqref="P4:P9">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2994,7 +2994,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q43">
+  <conditionalFormatting sqref="Q4:Q9">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -3006,7 +3006,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R4:R43">
+  <conditionalFormatting sqref="R4:R9">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -3018,8 +3018,968 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S43">
+  <conditionalFormatting sqref="S4:S9">
     <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10:D15">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:E15">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10:F15">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10:G15">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10:H15">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10:I15">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J10:J15">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10:K15">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L10:L15">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M10:M15">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N10:N15">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O10:O15">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P10:P15">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q10:Q15">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R10:R15">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S10:S15">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:D21">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:E21">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:F21">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16:G21">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16:H21">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16:I21">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16:J21">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16:K21">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L16:L21">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M16:M21">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N16:N21">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O16:O21">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P16:P21">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q16:Q21">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R16:R21">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S16:S21">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D27">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E27">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F27">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G27">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:H27">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I27">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22:J27">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K22:K27">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L22:L27">
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M22:M27">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22:N27">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O22:O27">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22:P27">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q22:Q27">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R22:R27">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S22:S27">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28:D33">
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28:E33">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F33">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:G33">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28:H33">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28:I33">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28:J33">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28:K33">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L28:L33">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M28:M33">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N28:N33">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O28:O33">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P28:P33">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q28:Q33">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R28:R33">
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S28:S33">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34:D43">
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34:E43">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34:F43">
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G43">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34:H43">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I34:I43">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J34:J43">
+    <cfRule type="colorScale" priority="87">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34:K43">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L34:L43">
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M34:M43">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N34:N43">
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O34:O43">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P34:P43">
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q34:Q43">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R34:R43">
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S34:S43">
+    <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2827,6 +2827,137 @@
       <c r="R43" s="7" t="n"/>
       <c r="S43" s="7" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>P0B</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="6" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="P44" s="7" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="7" t="n"/>
+      <c r="S44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="P45" s="7" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="7" t="n"/>
+      <c r="S45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="7" t="n"/>
+      <c r="S46" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="H1:K1"/>
@@ -3990,6 +4121,198 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D44:D46">
+    <cfRule type="colorScale" priority="97">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E44:E46">
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F44:F46">
+    <cfRule type="colorScale" priority="99">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:G46">
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H44:H46">
+    <cfRule type="colorScale" priority="101">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I44:I46">
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J44:J46">
+    <cfRule type="colorScale" priority="103">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K44:K46">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L44:L46">
+    <cfRule type="colorScale" priority="105">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M44:M46">
+    <cfRule type="colorScale" priority="106">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N44:N46">
+    <cfRule type="colorScale" priority="107">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O44:O46">
+    <cfRule type="colorScale" priority="108">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P44:P46">
+    <cfRule type="colorScale" priority="109">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q44:Q46">
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R44:R46">
+    <cfRule type="colorScale" priority="111">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S44:S46">
+    <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2877,40 +2877,48 @@
       <c r="S44" s="7" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>P0C</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.089</v>
+        <v>0.053</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.273</v>
+        <v>0.209</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.242</v>
+        <v>0.189</v>
       </c>
       <c r="H45" s="7" t="n"/>
       <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
       <c r="K45" s="7" t="n"/>
       <c r="L45" s="6" t="n">
-        <v>0.15</v>
+        <v>0.135</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.168</v>
+        <v>0.132</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.321</v>
+        <v>0.335</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0.189</v>
+        <v>0.205</v>
       </c>
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="n"/>
@@ -2918,11 +2926,19 @@
       <c r="S45" s="7" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n"/>
-      <c r="B46" s="5" t="n"/>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>P0B</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>abde</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
@@ -2957,6 +2973,153 @@
       <c r="Q46" s="7" t="n"/>
       <c r="R46" s="7" t="n"/>
       <c r="S46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>P0C</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M47" s="6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P47" s="7" t="n"/>
+      <c r="Q47" s="7" t="n"/>
+      <c r="R47" s="7" t="n"/>
+      <c r="S47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>P0B</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="N48" s="6" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="P48" s="7" t="n"/>
+      <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="7" t="n"/>
+      <c r="S48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>P0C</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P49" s="7" t="n"/>
+      <c r="Q49" s="7" t="n"/>
+      <c r="R49" s="7" t="n"/>
+      <c r="S49" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4121,7 +4284,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D44:D46">
+  <conditionalFormatting sqref="D44">
     <cfRule type="colorScale" priority="97">
       <colorScale>
         <cfvo type="min"/>
@@ -4133,7 +4296,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E44:E46">
+  <conditionalFormatting sqref="E44">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -4145,7 +4308,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F44:F46">
+  <conditionalFormatting sqref="F44">
     <cfRule type="colorScale" priority="99">
       <colorScale>
         <cfvo type="min"/>
@@ -4157,7 +4320,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G44:G46">
+  <conditionalFormatting sqref="G44">
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min"/>
@@ -4169,7 +4332,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H44:H46">
+  <conditionalFormatting sqref="H44">
     <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
@@ -4181,7 +4344,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I44:I46">
+  <conditionalFormatting sqref="I44">
     <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min"/>
@@ -4193,7 +4356,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J44:J46">
+  <conditionalFormatting sqref="J44">
     <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
@@ -4205,7 +4368,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44:K46">
+  <conditionalFormatting sqref="K44">
     <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
@@ -4217,7 +4380,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L44:L46">
+  <conditionalFormatting sqref="L44">
     <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
@@ -4229,7 +4392,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44:M46">
+  <conditionalFormatting sqref="M44">
     <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
@@ -4241,7 +4404,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N44:N46">
+  <conditionalFormatting sqref="N44">
     <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
@@ -4253,7 +4416,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O44:O46">
+  <conditionalFormatting sqref="O44">
     <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min"/>
@@ -4265,7 +4428,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P44:P46">
+  <conditionalFormatting sqref="P44">
     <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
@@ -4277,7 +4440,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q44:Q46">
+  <conditionalFormatting sqref="Q44">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="min"/>
@@ -4289,7 +4452,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R44:R46">
+  <conditionalFormatting sqref="R44">
     <cfRule type="colorScale" priority="111">
       <colorScale>
         <cfvo type="min"/>
@@ -4301,8 +4464,968 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S44:S46">
+  <conditionalFormatting sqref="S44">
     <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D45">
+    <cfRule type="colorScale" priority="113">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45">
+    <cfRule type="colorScale" priority="114">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F45">
+    <cfRule type="colorScale" priority="115">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G45">
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H45">
+    <cfRule type="colorScale" priority="117">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I45">
+    <cfRule type="colorScale" priority="118">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J45">
+    <cfRule type="colorScale" priority="119">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45">
+    <cfRule type="colorScale" priority="120">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L45">
+    <cfRule type="colorScale" priority="121">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M45">
+    <cfRule type="colorScale" priority="122">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N45">
+    <cfRule type="colorScale" priority="123">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O45">
+    <cfRule type="colorScale" priority="124">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P45">
+    <cfRule type="colorScale" priority="125">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q45">
+    <cfRule type="colorScale" priority="126">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R45">
+    <cfRule type="colorScale" priority="127">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S45">
+    <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D46">
+    <cfRule type="colorScale" priority="129">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E46">
+    <cfRule type="colorScale" priority="130">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F46">
+    <cfRule type="colorScale" priority="131">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G46">
+    <cfRule type="colorScale" priority="132">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H46">
+    <cfRule type="colorScale" priority="133">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46">
+    <cfRule type="colorScale" priority="134">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J46">
+    <cfRule type="colorScale" priority="135">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K46">
+    <cfRule type="colorScale" priority="136">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L46">
+    <cfRule type="colorScale" priority="137">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M46">
+    <cfRule type="colorScale" priority="138">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N46">
+    <cfRule type="colorScale" priority="139">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O46">
+    <cfRule type="colorScale" priority="140">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P46">
+    <cfRule type="colorScale" priority="141">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q46">
+    <cfRule type="colorScale" priority="142">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R46">
+    <cfRule type="colorScale" priority="143">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S46">
+    <cfRule type="colorScale" priority="144">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47">
+    <cfRule type="colorScale" priority="145">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E47">
+    <cfRule type="colorScale" priority="146">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47">
+    <cfRule type="colorScale" priority="147">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G47">
+    <cfRule type="colorScale" priority="148">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H47">
+    <cfRule type="colorScale" priority="149">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I47">
+    <cfRule type="colorScale" priority="150">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J47">
+    <cfRule type="colorScale" priority="151">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K47">
+    <cfRule type="colorScale" priority="152">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L47">
+    <cfRule type="colorScale" priority="153">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M47">
+    <cfRule type="colorScale" priority="154">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N47">
+    <cfRule type="colorScale" priority="155">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O47">
+    <cfRule type="colorScale" priority="156">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P47">
+    <cfRule type="colorScale" priority="157">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q47">
+    <cfRule type="colorScale" priority="158">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R47">
+    <cfRule type="colorScale" priority="159">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S47">
+    <cfRule type="colorScale" priority="160">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D48">
+    <cfRule type="colorScale" priority="161">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E48">
+    <cfRule type="colorScale" priority="162">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48">
+    <cfRule type="colorScale" priority="163">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G48">
+    <cfRule type="colorScale" priority="164">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H48">
+    <cfRule type="colorScale" priority="165">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I48">
+    <cfRule type="colorScale" priority="166">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48">
+    <cfRule type="colorScale" priority="167">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K48">
+    <cfRule type="colorScale" priority="168">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L48">
+    <cfRule type="colorScale" priority="169">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M48">
+    <cfRule type="colorScale" priority="170">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N48">
+    <cfRule type="colorScale" priority="171">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O48">
+    <cfRule type="colorScale" priority="172">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P48">
+    <cfRule type="colorScale" priority="173">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q48">
+    <cfRule type="colorScale" priority="174">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R48">
+    <cfRule type="colorScale" priority="175">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S48">
+    <cfRule type="colorScale" priority="176">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D49">
+    <cfRule type="colorScale" priority="177">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E49">
+    <cfRule type="colorScale" priority="178">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49">
+    <cfRule type="colorScale" priority="179">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G49">
+    <cfRule type="colorScale" priority="180">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H49">
+    <cfRule type="colorScale" priority="181">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I49">
+    <cfRule type="colorScale" priority="182">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J49">
+    <cfRule type="colorScale" priority="183">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K49">
+    <cfRule type="colorScale" priority="184">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L49">
+    <cfRule type="colorScale" priority="185">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M49">
+    <cfRule type="colorScale" priority="186">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N49">
+    <cfRule type="colorScale" priority="187">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O49">
+    <cfRule type="colorScale" priority="188">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P49">
+    <cfRule type="colorScale" priority="189">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q49">
+    <cfRule type="colorScale" priority="190">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R49">
+    <cfRule type="colorScale" priority="191">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S49">
+    <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1354,12 +1354,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0B</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1368,53 +1368,37 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.033</v>
+        <v>0.089</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.032</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.196</v>
+        <v>0.273</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0.354</v>
-      </c>
+        <v>0.242</v>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
       <c r="L16" s="6" t="n">
-        <v>0.036</v>
+        <v>0.147</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.029</v>
+        <v>0.164</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.258</v>
+        <v>0.333</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="S16" s="6" t="n">
-        <v>0.251</v>
-      </c>
+        <v>0.197</v>
+      </c>
+      <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1425,53 +1409,37 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.045</v>
+        <v>0.089</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.046</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.207</v>
+        <v>0.273</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0.271</v>
-      </c>
+        <v>0.242</v>
+      </c>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
       <c r="L17" s="6" t="n">
-        <v>0.037</v>
+        <v>0.15</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.031</v>
+        <v>0.168</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.253</v>
+        <v>0.321</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0.254</v>
-      </c>
+        <v>0.189</v>
+      </c>
+      <c r="P17" s="7" t="n"/>
+      <c r="Q17" s="7" t="n"/>
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1482,56 +1450,44 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.045</v>
+        <v>0.089</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.046</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.207</v>
+        <v>0.273</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>0.271</v>
-      </c>
+        <v>0.242</v>
+      </c>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
       <c r="L18" s="6" t="n">
-        <v>0.037</v>
+        <v>0.15</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.031</v>
+        <v>0.168</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.253</v>
+        <v>0.321</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="S18" s="6" t="n">
-        <v>0.254</v>
-      </c>
+        <v>0.189</v>
+      </c>
+      <c r="P18" s="7" t="n"/>
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>P0C</t>
+        </is>
+      </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
           <t>sent</t>
@@ -1543,53 +1499,37 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.257</v>
+        <v>0.209</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0.265</v>
-      </c>
+        <v>0.189</v>
+      </c>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
       <c r="L19" s="6" t="n">
-        <v>0.067</v>
+        <v>0.135</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.052</v>
+        <v>0.132</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.283</v>
+        <v>0.335</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>0.301</v>
-      </c>
+        <v>0.205</v>
+      </c>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="7" t="n"/>
+      <c r="S19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1600,53 +1540,37 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.044</v>
+        <v>0.04</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.259</v>
+        <v>0.21</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0.17</v>
-      </c>
+        <v>0.191</v>
+      </c>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
       <c r="L20" s="6" t="n">
-        <v>0.068</v>
+        <v>0.135</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.054</v>
+        <v>0.135</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.275</v>
+        <v>0.333</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0.302</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="7" t="n"/>
+      <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="7" t="n"/>
+      <c r="S20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1657,58 +1581,42 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.044</v>
+        <v>0.04</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.259</v>
+        <v>0.21</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0.17</v>
-      </c>
+        <v>0.191</v>
+      </c>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
       <c r="L21" s="6" t="n">
-        <v>0.068</v>
+        <v>0.135</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.054</v>
+        <v>0.135</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.275</v>
+        <v>0.333</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0.302</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="7" t="n"/>
+      <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="7" t="n"/>
+      <c r="S21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1722,52 +1630,52 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.179</v>
+        <v>0.196</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.132</v>
+        <v>0.161</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.098</v>
+        <v>0.104</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.355</v>
+        <v>0.435</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.309</v>
+        <v>0.354</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.059</v>
+        <v>0.036</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.054</v>
+        <v>0.029</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.388</v>
+        <v>0.258</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.209</v>
+        <v>0.177</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0.206</v>
+        <v>0.177</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>0.403</v>
+        <v>0.441</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.241</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="23">
@@ -1779,52 +1687,52 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.189</v>
+        <v>0.207</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.336</v>
+        <v>0.383</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.231</v>
+        <v>0.271</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.062</v>
+        <v>0.037</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.057</v>
+        <v>0.031</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.396</v>
+        <v>0.253</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.282</v>
+        <v>0.162</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.209</v>
+        <v>0.23</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.206</v>
+        <v>0.249</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0.403</v>
+        <v>0.447</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="24">
@@ -1836,52 +1744,52 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.189</v>
+        <v>0.207</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.336</v>
+        <v>0.383</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.231</v>
+        <v>0.271</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.062</v>
+        <v>0.037</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.057</v>
+        <v>0.031</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.396</v>
+        <v>0.253</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.282</v>
+        <v>0.162</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.209</v>
+        <v>0.23</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>0.206</v>
+        <v>0.249</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>0.403</v>
+        <v>0.447</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="25">
@@ -1897,52 +1805,52 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.098</v>
+        <v>0.052</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.115</v>
+        <v>0.042</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.304</v>
+        <v>0.257</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.165</v>
+        <v>0.179</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.037</v>
+        <v>0.111</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.029</v>
+        <v>0.081</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.543</v>
+        <v>0.293</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.438</v>
+        <v>0.265</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.125</v>
+        <v>0.067</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.15</v>
+        <v>0.052</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.422</v>
+        <v>0.283</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.187</v>
+        <v>0.189</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.28</v>
+        <v>0.224</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.265</v>
+        <v>0.226</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>0.387</v>
+        <v>0.419</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>0.278</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="26">
@@ -1954,52 +1862,52 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.098</v>
+        <v>0.053</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.115</v>
+        <v>0.044</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.303</v>
+        <v>0.259</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.16</v>
+        <v>0.183</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.039</v>
+        <v>0.119</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.03</v>
+        <v>0.092</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.491</v>
+        <v>0.252</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.319</v>
+        <v>0.17</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.126</v>
+        <v>0.068</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.153</v>
+        <v>0.054</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.423</v>
+        <v>0.275</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.186</v>
+        <v>0.181</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.28</v>
+        <v>0.227</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0.265</v>
+        <v>0.231</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>0.387</v>
+        <v>0.421</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0.278</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="27">
@@ -2011,58 +1919,58 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.098</v>
+        <v>0.053</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.115</v>
+        <v>0.044</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.303</v>
+        <v>0.259</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.16</v>
+        <v>0.183</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.039</v>
+        <v>0.119</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.03</v>
+        <v>0.092</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.491</v>
+        <v>0.252</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.319</v>
+        <v>0.17</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.126</v>
+        <v>0.068</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.153</v>
+        <v>0.054</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.423</v>
+        <v>0.275</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.186</v>
+        <v>0.181</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.28</v>
+        <v>0.227</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.265</v>
+        <v>0.231</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>0.387</v>
+        <v>0.421</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0.278</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2076,52 +1984,52 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.113</v>
+        <v>0.179</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.04</v>
+        <v>0.098</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.039</v>
+        <v>0.076</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.628</v>
+        <v>0.355</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.303</v>
+        <v>0.309</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.294</v>
+        <v>0.388</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.122</v>
+        <v>0.209</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0.12</v>
+        <v>0.206</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>0.547</v>
+        <v>0.403</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0.275</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="29">
@@ -2133,52 +2041,52 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.112</v>
+        <v>0.189</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.058</v>
+        <v>0.11</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.066</v>
+        <v>0.09</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.161</v>
+        <v>0.231</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.293</v>
+        <v>0.396</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.172</v>
+        <v>0.282</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.334</v>
+        <v>0.209</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.409</v>
+        <v>0.206</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>0.509</v>
+        <v>0.403</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.181</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="30">
@@ -2190,52 +2098,52 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.112</v>
+        <v>0.189</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.058</v>
+        <v>0.11</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.066</v>
+        <v>0.09</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.161</v>
+        <v>0.231</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.293</v>
+        <v>0.396</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.172</v>
+        <v>0.282</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.334</v>
+        <v>0.209</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0.409</v>
+        <v>0.206</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>0.509</v>
+        <v>0.403</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0.181</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="31">
@@ -2251,52 +2159,52 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0.128</v>
+        <v>0.098</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.145</v>
+        <v>0.115</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.333</v>
+        <v>0.304</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.212</v>
+        <v>0.165</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.055</v>
+        <v>0.029</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.5</v>
+        <v>0.543</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.157</v>
+        <v>0.438</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.228</v>
+        <v>0.125</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.233</v>
+        <v>0.15</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.363</v>
+        <v>0.422</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.19</v>
+        <v>0.187</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.319</v>
+        <v>0.28</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0.309</v>
+        <v>0.265</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>0.439</v>
+        <v>0.387</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.269</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="32">
@@ -2308,52 +2216,52 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.128</v>
+        <v>0.098</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.145</v>
+        <v>0.115</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.332</v>
+        <v>0.303</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.212</v>
+        <v>0.16</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.077</v>
+        <v>0.039</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.099</v>
+        <v>0.03</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.515</v>
+        <v>0.491</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.181</v>
+        <v>0.319</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.231</v>
+        <v>0.126</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.238</v>
+        <v>0.153</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.351</v>
+        <v>0.423</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.358</v>
+        <v>0.28</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0.359</v>
+        <v>0.265</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>0.409</v>
+        <v>0.387</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>0.234</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="33">
@@ -2365,58 +2273,58 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.128</v>
+        <v>0.098</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.145</v>
+        <v>0.115</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.332</v>
+        <v>0.303</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.212</v>
+        <v>0.16</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.077</v>
+        <v>0.039</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.099</v>
+        <v>0.03</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.515</v>
+        <v>0.491</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.181</v>
+        <v>0.319</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.231</v>
+        <v>0.126</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.238</v>
+        <v>0.153</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.351</v>
+        <v>0.423</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0.358</v>
+        <v>0.28</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.359</v>
+        <v>0.265</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>0.409</v>
+        <v>0.387</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>0.234</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -2430,52 +2338,52 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>0.012</v>
+        <v>0.036</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.129</v>
+        <v>0.113</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.129</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.095</v>
+        <v>0.04</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.068</v>
+        <v>0.039</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.529</v>
+        <v>0.628</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.436</v>
+        <v>0.303</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.031</v>
+        <v>0.052</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.022</v>
+        <v>0.05</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.309</v>
+        <v>0.294</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.244</v>
+        <v>0.17</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.128</v>
+        <v>0.122</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>0.148</v>
+        <v>0.12</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>0.491</v>
+        <v>0.547</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0.28</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="35">
@@ -2487,52 +2395,52 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.012</v>
+        <v>0.036</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.129</v>
+        <v>0.112</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.129</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.128</v>
+        <v>0.058</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.111</v>
+        <v>0.066</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.467</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.319</v>
+        <v>0.161</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.031</v>
+        <v>0.053</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.022</v>
+        <v>0.052</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.309</v>
+        <v>0.293</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.244</v>
+        <v>0.172</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>0.142</v>
+        <v>0.334</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0.189</v>
+        <v>0.409</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>0.505</v>
+        <v>0.509</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0.249</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="36">
@@ -2544,52 +2452,52 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.012</v>
+        <v>0.036</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.129</v>
+        <v>0.112</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.129</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.128</v>
+        <v>0.058</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.111</v>
+        <v>0.066</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.467</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.319</v>
+        <v>0.161</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.031</v>
+        <v>0.053</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.022</v>
+        <v>0.052</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.304</v>
+        <v>0.293</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.241</v>
+        <v>0.172</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.142</v>
+        <v>0.334</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>0.189</v>
+        <v>0.409</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>0.505</v>
+        <v>0.509</v>
       </c>
       <c r="S36" s="6" t="n">
-        <v>0.249</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="37">
@@ -2601,132 +2509,236 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>ordered</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>0.157</v>
+      </c>
       <c r="L37" s="6" t="n">
-        <v/>
+        <v>0.228</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v/>
+        <v>0.233</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v/>
+        <v>0.363</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="7" t="n"/>
-      <c r="Q37" s="7" t="n"/>
-      <c r="R37" s="7" t="n"/>
-      <c r="S37" s="7" t="n"/>
+        <v>0.19</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0.269</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>0.181</v>
+      </c>
       <c r="L38" s="6" t="n">
-        <v/>
+        <v>0.231</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v/>
+        <v>0.238</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v/>
+        <v>0.351</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="7" t="n"/>
-      <c r="Q38" s="7" t="n"/>
-      <c r="R38" s="7" t="n"/>
-      <c r="S38" s="7" t="n"/>
+        <v>0.182</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="S38" s="6" t="n">
+        <v>0.234</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="7" t="n"/>
-      <c r="J39" s="7" t="n"/>
-      <c r="K39" s="7" t="n"/>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>0.181</v>
+      </c>
       <c r="L39" s="6" t="n">
-        <v/>
+        <v>0.231</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v/>
+        <v>0.238</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v/>
+        <v>0.351</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="7" t="n"/>
-      <c r="Q39" s="7" t="n"/>
-      <c r="R39" s="7" t="n"/>
-      <c r="S39" s="7" t="n"/>
+        <v>0.182</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0.234</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>ab</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="7" t="n"/>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>0.436</v>
+      </c>
       <c r="L40" s="6" t="n">
-        <v/>
+        <v>0.031</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v/>
+        <v>0.022</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v/>
+        <v>0.309</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="7" t="n"/>
-      <c r="Q40" s="7" t="n"/>
-      <c r="R40" s="7" t="n"/>
-      <c r="S40" s="7" t="n"/>
+        <v>0.244</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -2736,390 +2748,111 @@
           <t>abde</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
+      <c r="D41" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>0.319</v>
+      </c>
       <c r="L41" s="6" t="n">
-        <v/>
+        <v>0.031</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v/>
+        <v>0.022</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v/>
+        <v>0.309</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="7" t="n"/>
-      <c r="Q41" s="7" t="n"/>
-      <c r="R41" s="7" t="n"/>
-      <c r="S41" s="7" t="n"/>
+        <v>0.244</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0.249</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="7" t="n"/>
-      <c r="J42" s="7" t="n"/>
-      <c r="K42" s="7" t="n"/>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>0.319</v>
+      </c>
       <c r="L42" s="6" t="n">
-        <v/>
+        <v>0.031</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v/>
+        <v>0.022</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v/>
+        <v>0.304</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="7" t="n"/>
-      <c r="Q42" s="7" t="n"/>
-      <c r="R42" s="7" t="n"/>
-      <c r="S42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n"/>
-      <c r="J43" s="7" t="n"/>
-      <c r="K43" s="7" t="n"/>
-      <c r="L43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="O43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="7" t="n"/>
-      <c r="Q43" s="7" t="n"/>
-      <c r="R43" s="7" t="n"/>
-      <c r="S43" s="7" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>P0B</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
-      <c r="J44" s="7" t="n"/>
-      <c r="K44" s="7" t="n"/>
-      <c r="L44" s="6" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="M44" s="6" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="N44" s="6" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O44" s="6" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="P44" s="7" t="n"/>
-      <c r="Q44" s="7" t="n"/>
-      <c r="R44" s="7" t="n"/>
-      <c r="S44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>P0C</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="G45" s="6" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="Q42" s="6" t="n">
         <v>0.189</v>
       </c>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
-      <c r="J45" s="7" t="n"/>
-      <c r="K45" s="7" t="n"/>
-      <c r="L45" s="6" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="M45" s="6" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="O45" s="6" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="P45" s="7" t="n"/>
-      <c r="Q45" s="7" t="n"/>
-      <c r="R45" s="7" t="n"/>
-      <c r="S45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>P0B</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>abde</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="E46" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="G46" s="6" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="K46" s="7" t="n"/>
-      <c r="L46" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M46" s="6" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="N46" s="6" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="P46" s="7" t="n"/>
-      <c r="Q46" s="7" t="n"/>
-      <c r="R46" s="7" t="n"/>
-      <c r="S46" s="7" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>P0C</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>abde</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="7" t="n"/>
-      <c r="K47" s="7" t="n"/>
-      <c r="L47" s="6" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="M47" s="6" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="N47" s="6" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O47" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P47" s="7" t="n"/>
-      <c r="Q47" s="7" t="n"/>
-      <c r="R47" s="7" t="n"/>
-      <c r="S47" s="7" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>P0B</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-      <c r="J48" s="7" t="n"/>
-      <c r="K48" s="7" t="n"/>
-      <c r="L48" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M48" s="6" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="N48" s="6" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="O48" s="6" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="P48" s="7" t="n"/>
-      <c r="Q48" s="7" t="n"/>
-      <c r="R48" s="7" t="n"/>
-      <c r="S48" s="7" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>P0C</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>sent</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n"/>
-      <c r="L49" s="6" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O49" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P49" s="7" t="n"/>
-      <c r="Q49" s="7" t="n"/>
-      <c r="R49" s="7" t="n"/>
-      <c r="S49" s="7" t="n"/>
+      <c r="R42" s="6" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>0.249</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3516,7 +3249,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D21">
+  <conditionalFormatting sqref="D16:D18">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -3528,7 +3261,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E21">
+  <conditionalFormatting sqref="E16:E18">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -3540,7 +3273,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F21">
+  <conditionalFormatting sqref="F16:F18">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -3552,7 +3285,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G21">
+  <conditionalFormatting sqref="G16:G18">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -3564,7 +3297,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16:H21">
+  <conditionalFormatting sqref="H16:H18">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -3576,7 +3309,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16:I21">
+  <conditionalFormatting sqref="I16:I18">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
@@ -3588,7 +3321,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J16:J21">
+  <conditionalFormatting sqref="J16:J18">
     <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
@@ -3600,7 +3333,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K16:K21">
+  <conditionalFormatting sqref="K16:K18">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
@@ -3612,7 +3345,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L16:L21">
+  <conditionalFormatting sqref="L16:L18">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -3624,7 +3357,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M16:M21">
+  <conditionalFormatting sqref="M16:M18">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -3636,7 +3369,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N16:N21">
+  <conditionalFormatting sqref="N16:N18">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
@@ -3648,7 +3381,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O16:O21">
+  <conditionalFormatting sqref="O16:O18">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
@@ -3660,7 +3393,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P16:P21">
+  <conditionalFormatting sqref="P16:P18">
     <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
@@ -3672,7 +3405,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q16:Q21">
+  <conditionalFormatting sqref="Q16:Q18">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -3684,7 +3417,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R16:R21">
+  <conditionalFormatting sqref="R16:R18">
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -3696,7 +3429,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S16:S21">
+  <conditionalFormatting sqref="S16:S18">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
@@ -3708,8 +3441,200 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D19:D21">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:E21">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:F21">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:G21">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19:H21">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19:I21">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19:J21">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K19:K21">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19:L21">
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19:M21">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19:N21">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O19:O21">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P19:P21">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q19:Q21">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R19:R21">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S19:S21">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D22:D27">
-    <cfRule type="colorScale" priority="49">
+    <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3721,7 +3646,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:E27">
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3733,7 +3658,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F27">
-    <cfRule type="colorScale" priority="51">
+    <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3745,7 +3670,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22:G27">
-    <cfRule type="colorScale" priority="52">
+    <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3757,7 +3682,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:H27">
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3769,7 +3694,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I27">
-    <cfRule type="colorScale" priority="54">
+    <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3781,7 +3706,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22:J27">
-    <cfRule type="colorScale" priority="55">
+    <cfRule type="colorScale" priority="71">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3793,7 +3718,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:K27">
-    <cfRule type="colorScale" priority="56">
+    <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3805,7 +3730,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L22:L27">
-    <cfRule type="colorScale" priority="57">
+    <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3817,7 +3742,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:M27">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3829,7 +3754,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22:N27">
-    <cfRule type="colorScale" priority="59">
+    <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3841,7 +3766,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22:O27">
-    <cfRule type="colorScale" priority="60">
+    <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3853,7 +3778,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22:P27">
-    <cfRule type="colorScale" priority="61">
+    <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3865,7 +3790,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q22:Q27">
-    <cfRule type="colorScale" priority="62">
+    <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3877,7 +3802,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R22:R27">
-    <cfRule type="colorScale" priority="63">
+    <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3889,7 +3814,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S22:S27">
-    <cfRule type="colorScale" priority="64">
+    <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3901,7 +3826,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28:D33">
-    <cfRule type="colorScale" priority="65">
+    <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3913,7 +3838,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E33">
-    <cfRule type="colorScale" priority="66">
+    <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3925,7 +3850,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28:F33">
-    <cfRule type="colorScale" priority="67">
+    <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3937,7 +3862,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:G33">
-    <cfRule type="colorScale" priority="68">
+    <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3949,7 +3874,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:H33">
-    <cfRule type="colorScale" priority="69">
+    <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3961,7 +3886,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28:I33">
-    <cfRule type="colorScale" priority="70">
+    <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3973,7 +3898,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J28:J33">
-    <cfRule type="colorScale" priority="71">
+    <cfRule type="colorScale" priority="87">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3985,7 +3910,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28:K33">
-    <cfRule type="colorScale" priority="72">
+    <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3997,7 +3922,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L28:L33">
-    <cfRule type="colorScale" priority="73">
+    <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4009,7 +3934,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M28:M33">
-    <cfRule type="colorScale" priority="74">
+    <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4021,7 +3946,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28:N33">
-    <cfRule type="colorScale" priority="75">
+    <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4033,7 +3958,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O28:O33">
-    <cfRule type="colorScale" priority="76">
+    <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4045,7 +3970,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P28:P33">
-    <cfRule type="colorScale" priority="77">
+    <cfRule type="colorScale" priority="93">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4057,7 +3982,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q28:Q33">
-    <cfRule type="colorScale" priority="78">
+    <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4069,7 +3994,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R28:R33">
-    <cfRule type="colorScale" priority="79">
+    <cfRule type="colorScale" priority="95">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4081,198 +4006,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S28:S33">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D34:D43">
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E34:E43">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F34:F43">
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G43">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H43">
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I34:I43">
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J43">
-    <cfRule type="colorScale" priority="87">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34:K43">
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L34:L43">
-    <cfRule type="colorScale" priority="89">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M34:M43">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N34:N43">
-    <cfRule type="colorScale" priority="91">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O34:O43">
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P34:P43">
-    <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q34:Q43">
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R34:R43">
-    <cfRule type="colorScale" priority="95">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S34:S43">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
@@ -4284,7 +4017,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D44">
+  <conditionalFormatting sqref="D34:D39">
     <cfRule type="colorScale" priority="97">
       <colorScale>
         <cfvo type="min"/>
@@ -4296,7 +4029,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E44">
+  <conditionalFormatting sqref="E34:E39">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -4308,7 +4041,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F44">
+  <conditionalFormatting sqref="F34:F39">
     <cfRule type="colorScale" priority="99">
       <colorScale>
         <cfvo type="min"/>
@@ -4320,7 +4053,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G44">
+  <conditionalFormatting sqref="G34:G39">
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min"/>
@@ -4332,7 +4065,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H44">
+  <conditionalFormatting sqref="H34:H39">
     <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
@@ -4344,7 +4077,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I44">
+  <conditionalFormatting sqref="I34:I39">
     <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min"/>
@@ -4356,7 +4089,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J44">
+  <conditionalFormatting sqref="J34:J39">
     <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
@@ -4368,7 +4101,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
+  <conditionalFormatting sqref="K34:K39">
     <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
@@ -4380,7 +4113,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L44">
+  <conditionalFormatting sqref="L34:L39">
     <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
@@ -4392,7 +4125,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44">
+  <conditionalFormatting sqref="M34:M39">
     <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
@@ -4404,7 +4137,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N44">
+  <conditionalFormatting sqref="N34:N39">
     <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
@@ -4416,7 +4149,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O44">
+  <conditionalFormatting sqref="O34:O39">
     <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min"/>
@@ -4428,7 +4161,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P44">
+  <conditionalFormatting sqref="P34:P39">
     <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
@@ -4440,7 +4173,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q44">
+  <conditionalFormatting sqref="Q34:Q39">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="min"/>
@@ -4452,7 +4185,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R44">
+  <conditionalFormatting sqref="R34:R39">
     <cfRule type="colorScale" priority="111">
       <colorScale>
         <cfvo type="min"/>
@@ -4464,7 +4197,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S44">
+  <conditionalFormatting sqref="S34:S39">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="min"/>
@@ -4476,7 +4209,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D45">
+  <conditionalFormatting sqref="D40:D42">
     <cfRule type="colorScale" priority="113">
       <colorScale>
         <cfvo type="min"/>
@@ -4488,7 +4221,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
+  <conditionalFormatting sqref="E40:E42">
     <cfRule type="colorScale" priority="114">
       <colorScale>
         <cfvo type="min"/>
@@ -4500,7 +4233,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F45">
+  <conditionalFormatting sqref="F40:F42">
     <cfRule type="colorScale" priority="115">
       <colorScale>
         <cfvo type="min"/>
@@ -4512,7 +4245,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G45">
+  <conditionalFormatting sqref="G40:G42">
     <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="min"/>
@@ -4524,7 +4257,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H45">
+  <conditionalFormatting sqref="H40:H42">
     <cfRule type="colorScale" priority="117">
       <colorScale>
         <cfvo type="min"/>
@@ -4536,7 +4269,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I45">
+  <conditionalFormatting sqref="I40:I42">
     <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min"/>
@@ -4548,7 +4281,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J45">
+  <conditionalFormatting sqref="J40:J42">
     <cfRule type="colorScale" priority="119">
       <colorScale>
         <cfvo type="min"/>
@@ -4560,7 +4293,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
+  <conditionalFormatting sqref="K40:K42">
     <cfRule type="colorScale" priority="120">
       <colorScale>
         <cfvo type="min"/>
@@ -4572,7 +4305,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L45">
+  <conditionalFormatting sqref="L40:L42">
     <cfRule type="colorScale" priority="121">
       <colorScale>
         <cfvo type="min"/>
@@ -4584,7 +4317,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M45">
+  <conditionalFormatting sqref="M40:M42">
     <cfRule type="colorScale" priority="122">
       <colorScale>
         <cfvo type="min"/>
@@ -4596,7 +4329,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N45">
+  <conditionalFormatting sqref="N40:N42">
     <cfRule type="colorScale" priority="123">
       <colorScale>
         <cfvo type="min"/>
@@ -4608,7 +4341,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O45">
+  <conditionalFormatting sqref="O40:O42">
     <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="min"/>
@@ -4620,7 +4353,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P45">
+  <conditionalFormatting sqref="P40:P42">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -4632,7 +4365,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q45">
+  <conditionalFormatting sqref="Q40:Q42">
     <cfRule type="colorScale" priority="126">
       <colorScale>
         <cfvo type="min"/>
@@ -4644,7 +4377,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R45">
+  <conditionalFormatting sqref="R40:R42">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -4656,776 +4389,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S45">
+  <conditionalFormatting sqref="S40:S42">
     <cfRule type="colorScale" priority="128">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D46">
-    <cfRule type="colorScale" priority="129">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E46">
-    <cfRule type="colorScale" priority="130">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F46">
-    <cfRule type="colorScale" priority="131">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G46">
-    <cfRule type="colorScale" priority="132">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H46">
-    <cfRule type="colorScale" priority="133">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I46">
-    <cfRule type="colorScale" priority="134">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J46">
-    <cfRule type="colorScale" priority="135">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K46">
-    <cfRule type="colorScale" priority="136">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L46">
-    <cfRule type="colorScale" priority="137">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M46">
-    <cfRule type="colorScale" priority="138">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N46">
-    <cfRule type="colorScale" priority="139">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O46">
-    <cfRule type="colorScale" priority="140">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P46">
-    <cfRule type="colorScale" priority="141">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q46">
-    <cfRule type="colorScale" priority="142">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R46">
-    <cfRule type="colorScale" priority="143">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S46">
-    <cfRule type="colorScale" priority="144">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D47">
-    <cfRule type="colorScale" priority="145">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E47">
-    <cfRule type="colorScale" priority="146">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F47">
-    <cfRule type="colorScale" priority="147">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G47">
-    <cfRule type="colorScale" priority="148">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H47">
-    <cfRule type="colorScale" priority="149">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I47">
-    <cfRule type="colorScale" priority="150">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J47">
-    <cfRule type="colorScale" priority="151">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47">
-    <cfRule type="colorScale" priority="152">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L47">
-    <cfRule type="colorScale" priority="153">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M47">
-    <cfRule type="colorScale" priority="154">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N47">
-    <cfRule type="colorScale" priority="155">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O47">
-    <cfRule type="colorScale" priority="156">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P47">
-    <cfRule type="colorScale" priority="157">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q47">
-    <cfRule type="colorScale" priority="158">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R47">
-    <cfRule type="colorScale" priority="159">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S47">
-    <cfRule type="colorScale" priority="160">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D48">
-    <cfRule type="colorScale" priority="161">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E48">
-    <cfRule type="colorScale" priority="162">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F48">
-    <cfRule type="colorScale" priority="163">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G48">
-    <cfRule type="colorScale" priority="164">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H48">
-    <cfRule type="colorScale" priority="165">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I48">
-    <cfRule type="colorScale" priority="166">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J48">
-    <cfRule type="colorScale" priority="167">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K48">
-    <cfRule type="colorScale" priority="168">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L48">
-    <cfRule type="colorScale" priority="169">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M48">
-    <cfRule type="colorScale" priority="170">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N48">
-    <cfRule type="colorScale" priority="171">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O48">
-    <cfRule type="colorScale" priority="172">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P48">
-    <cfRule type="colorScale" priority="173">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q48">
-    <cfRule type="colorScale" priority="174">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R48">
-    <cfRule type="colorScale" priority="175">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S48">
-    <cfRule type="colorScale" priority="176">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D49">
-    <cfRule type="colorScale" priority="177">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E49">
-    <cfRule type="colorScale" priority="178">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F49">
-    <cfRule type="colorScale" priority="179">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G49">
-    <cfRule type="colorScale" priority="180">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H49">
-    <cfRule type="colorScale" priority="181">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49">
-    <cfRule type="colorScale" priority="182">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J49">
-    <cfRule type="colorScale" priority="183">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
-    <cfRule type="colorScale" priority="184">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L49">
-    <cfRule type="colorScale" priority="185">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M49">
-    <cfRule type="colorScale" priority="186">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N49">
-    <cfRule type="colorScale" priority="187">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O49">
-    <cfRule type="colorScale" priority="188">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P49">
-    <cfRule type="colorScale" priority="189">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q49">
-    <cfRule type="colorScale" priority="190">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R49">
-    <cfRule type="colorScale" priority="191">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S49">
-    <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,10 @@
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -520,6 +524,11 @@
           <t>Qwen</t>
         </is>
       </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="n"/>
@@ -542,6 +551,11 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
+          <t>14b</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
@@ -642,6 +656,26 @@
           <t>token_precision</t>
         </is>
       </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>token_recall</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>token_precision</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -695,16 +729,20 @@
       <c r="O4" s="6" t="n">
         <v>0.082</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="P4" s="7" t="n"/>
+      <c r="Q4" s="7" t="n"/>
+      <c r="R4" s="7" t="n"/>
+      <c r="S4" s="7" t="n"/>
+      <c r="T4" s="6" t="n">
         <v>0.221</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="U4" s="6" t="n">
         <v>0.307</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="V4" s="6" t="n">
         <v>0.671</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="W4" s="6" t="n">
         <v>0.172</v>
       </c>
     </row>
@@ -752,16 +790,20 @@
       <c r="O5" s="6" t="n">
         <v>0.082</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+      <c r="R5" s="7" t="n"/>
+      <c r="S5" s="7" t="n"/>
+      <c r="T5" s="6" t="n">
         <v>0.264</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="U5" s="6" t="n">
         <v>0.416</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="V5" s="6" t="n">
         <v>0.677</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="W5" s="6" t="n">
         <v>0.174</v>
       </c>
     </row>
@@ -809,16 +851,20 @@
       <c r="O6" s="6" t="n">
         <v>0.082</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="7" t="n"/>
+      <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="7" t="n"/>
+      <c r="S6" s="7" t="n"/>
+      <c r="T6" s="6" t="n">
         <v>0.264</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="U6" s="6" t="n">
         <v>0.416</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="V6" s="6" t="n">
         <v>0.677</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="W6" s="6" t="n">
         <v>0.174</v>
       </c>
     </row>
@@ -870,16 +916,20 @@
       <c r="O7" s="6" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="7" t="n"/>
+      <c r="T7" s="6" t="n">
         <v>0.407</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="U7" s="6" t="n">
         <v>0.751</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="V7" s="6" t="n">
         <v>0.761</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="W7" s="6" t="n">
         <v>0.122</v>
       </c>
     </row>
@@ -927,16 +977,20 @@
       <c r="O8" s="6" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="7" t="n"/>
+      <c r="T8" s="6" t="n">
         <v>0.407</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="U8" s="6" t="n">
         <v>0.751</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="V8" s="6" t="n">
         <v>0.761</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="W8" s="6" t="n">
         <v>0.122</v>
       </c>
     </row>
@@ -984,16 +1038,20 @@
       <c r="O9" s="6" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="6" t="n">
         <v>0.407</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="U9" s="6" t="n">
         <v>0.751</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="V9" s="6" t="n">
         <v>0.761</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="W9" s="6" t="n">
         <v>0.122</v>
       </c>
     </row>
@@ -1049,16 +1107,20 @@
       <c r="O10" s="6" t="n">
         <v>0.134</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="6" t="n">
         <v>0.134</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="U10" s="6" t="n">
         <v>0.143</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="V10" s="6" t="n">
         <v>0.596</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="W10" s="6" t="n">
         <v>0.213</v>
       </c>
     </row>
@@ -1106,16 +1168,20 @@
       <c r="O11" s="6" t="n">
         <v>0.118</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="6" t="n">
         <v>0.274</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="U11" s="6" t="n">
         <v>0.377</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="V11" s="6" t="n">
         <v>0.556</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="W11" s="6" t="n">
         <v>0.188</v>
       </c>
     </row>
@@ -1163,16 +1229,20 @@
       <c r="O12" s="6" t="n">
         <v>0.118</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="7" t="n"/>
+      <c r="T12" s="6" t="n">
         <v>0.274</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="U12" s="6" t="n">
         <v>0.377</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="V12" s="6" t="n">
         <v>0.556</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="W12" s="6" t="n">
         <v>0.188</v>
       </c>
     </row>
@@ -1224,16 +1294,20 @@
       <c r="O13" s="6" t="n">
         <v>0.144</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="6" t="n">
         <v>0.31</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="U13" s="6" t="n">
         <v>0.364</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="V13" s="6" t="n">
         <v>0.435</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="W13" s="6" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -1281,16 +1355,20 @@
       <c r="O14" s="6" t="n">
         <v>0.144</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="7" t="n"/>
+      <c r="T14" s="6" t="n">
         <v>0.319</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="U14" s="6" t="n">
         <v>0.374</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="V14" s="6" t="n">
         <v>0.429</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="W14" s="6" t="n">
         <v>0.234</v>
       </c>
     </row>
@@ -1338,16 +1416,20 @@
       <c r="O15" s="6" t="n">
         <v>0.144</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="6" t="n">
         <v>0.319</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="U15" s="6" t="n">
         <v>0.374</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="V15" s="6" t="n">
         <v>0.429</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="W15" s="6" t="n">
         <v>0.234</v>
       </c>
     </row>
@@ -1399,6 +1481,10 @@
       <c r="Q16" s="7" t="n"/>
       <c r="R16" s="7" t="n"/>
       <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1440,6 +1526,10 @@
       <c r="Q17" s="7" t="n"/>
       <c r="R17" s="7" t="n"/>
       <c r="S17" s="7" t="n"/>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
+      <c r="W17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1481,6 +1571,10 @@
       <c r="Q18" s="7" t="n"/>
       <c r="R18" s="7" t="n"/>
       <c r="S18" s="7" t="n"/>
+      <c r="T18" s="7" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
+      <c r="W18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1526,10 +1620,22 @@
       <c r="O19" s="6" t="n">
         <v>0.205</v>
       </c>
-      <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="7" t="n"/>
-      <c r="R19" s="7" t="n"/>
-      <c r="S19" s="7" t="n"/>
+      <c r="P19" s="6" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1567,10 +1673,22 @@
       <c r="O20" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="P20" s="7" t="n"/>
-      <c r="Q20" s="7" t="n"/>
-      <c r="R20" s="7" t="n"/>
-      <c r="S20" s="7" t="n"/>
+      <c r="P20" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="T20" s="7" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1608,20 +1726,32 @@
       <c r="O21" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="P21" s="7" t="n"/>
-      <c r="Q21" s="7" t="n"/>
-      <c r="R21" s="7" t="n"/>
-      <c r="S21" s="7" t="n"/>
+      <c r="P21" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0D</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1630,53 +1760,49 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.033</v>
+        <v>0.098</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.032</v>
+        <v>0.074</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.196</v>
+        <v>0.249</v>
       </c>
       <c r="G22" s="6" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="6" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="M22" s="6" t="n">
         <v>0.161</v>
       </c>
-      <c r="H22" s="6" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <v>0.029</v>
-      </c>
       <c r="N22" s="6" t="n">
-        <v>0.258</v>
+        <v>0.232</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.17</v>
+        <v>0.226</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.177</v>
+        <v>0.237</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0.177</v>
+        <v>0.223</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>0.441</v>
+        <v>0.403</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0.251</v>
-      </c>
+        <v>0.335</v>
+      </c>
+      <c r="T22" s="7" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="7" t="n"/>
+      <c r="W22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1687,53 +1813,49 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0.045</v>
+        <v>0.098</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.046</v>
+        <v>0.074</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.207</v>
+        <v>0.248</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0.271</v>
-      </c>
+        <v>0.226</v>
+      </c>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
       <c r="L23" s="6" t="n">
-        <v>0.037</v>
+        <v>0.194</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.031</v>
+        <v>0.164</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.253</v>
+        <v>0.233</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.162</v>
+        <v>0.225</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.249</v>
+        <v>0.223</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0.447</v>
+        <v>0.396</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0.254</v>
-      </c>
+        <v>0.324</v>
+      </c>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
+      <c r="W23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1744,59 +1866,59 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.045</v>
+        <v>0.098</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.046</v>
+        <v>0.074</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.207</v>
+        <v>0.248</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0.271</v>
-      </c>
+        <v>0.226</v>
+      </c>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
       <c r="L24" s="6" t="n">
-        <v>0.037</v>
+        <v>0.194</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.031</v>
+        <v>0.164</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.253</v>
+        <v>0.233</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.162</v>
+        <v>0.225</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>0.249</v>
+        <v>0.223</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>0.447</v>
+        <v>0.396</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0.254</v>
-      </c>
+        <v>0.324</v>
+      </c>
+      <c r="T24" s="7" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="7" t="n"/>
+      <c r="W24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1805,52 +1927,56 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.052</v>
+        <v>0.033</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.257</v>
+        <v>0.196</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.179</v>
+        <v>0.161</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.111</v>
+        <v>0.104</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.293</v>
+        <v>0.435</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.265</v>
+        <v>0.354</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.067</v>
+        <v>0.036</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.052</v>
+        <v>0.029</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.283</v>
+        <v>0.258</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="S25" s="6" t="n">
-        <v>0.301</v>
+        <v>0.17</v>
+      </c>
+      <c r="P25" s="7" t="n"/>
+      <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="7" t="n"/>
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="6" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="U25" s="6" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="W25" s="6" t="n">
+        <v>0.251</v>
       </c>
     </row>
     <row r="26">
@@ -1862,52 +1988,56 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.053</v>
+        <v>0.045</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.259</v>
+        <v>0.207</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.183</v>
+        <v>0.151</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0.119</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.252</v>
+        <v>0.383</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.17</v>
+        <v>0.271</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.068</v>
+        <v>0.037</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.054</v>
+        <v>0.031</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.275</v>
+        <v>0.253</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>0.302</v>
+        <v>0.162</v>
+      </c>
+      <c r="P26" s="7" t="n"/>
+      <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="7" t="n"/>
+      <c r="S26" s="7" t="n"/>
+      <c r="T26" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U26" s="6" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="V26" s="6" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="W26" s="6" t="n">
+        <v>0.254</v>
       </c>
     </row>
     <row r="27">
@@ -1919,63 +2049,63 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.053</v>
+        <v>0.045</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.259</v>
+        <v>0.207</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.183</v>
+        <v>0.151</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>0.119</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.252</v>
+        <v>0.383</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.17</v>
+        <v>0.271</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.068</v>
+        <v>0.037</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.054</v>
+        <v>0.031</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.275</v>
+        <v>0.253</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="S27" s="6" t="n">
-        <v>0.302</v>
+        <v>0.162</v>
+      </c>
+      <c r="P27" s="7" t="n"/>
+      <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="7" t="n"/>
+      <c r="S27" s="7" t="n"/>
+      <c r="T27" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U27" s="6" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="V27" s="6" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="W27" s="6" t="n">
+        <v>0.254</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1984,52 +2114,56 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.037</v>
+        <v>0.052</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="F28" s="6" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="G28" s="6" t="n">
         <v>0.179</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>0.132</v>
-      </c>
       <c r="H28" s="6" t="n">
-        <v>0.098</v>
+        <v>0.111</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.076</v>
+        <v>0.081</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.355</v>
+        <v>0.293</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.309</v>
+        <v>0.265</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0.059</v>
+        <v>0.067</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.388</v>
+        <v>0.283</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="S28" s="6" t="n">
-        <v>0.241</v>
+        <v>0.189</v>
+      </c>
+      <c r="P28" s="7" t="n"/>
+      <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="7" t="n"/>
+      <c r="S28" s="7" t="n"/>
+      <c r="T28" s="6" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="W28" s="6" t="n">
+        <v>0.301</v>
       </c>
     </row>
     <row r="29">
@@ -2041,52 +2175,56 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0.047</v>
+        <v>0.053</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>0.044</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.189</v>
+        <v>0.259</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.147</v>
+        <v>0.183</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.09</v>
+        <v>0.092</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.336</v>
+        <v>0.252</v>
       </c>
       <c r="K29" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="P29" s="7" t="n"/>
+      <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="7" t="n"/>
+      <c r="S29" s="7" t="n"/>
+      <c r="T29" s="6" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="U29" s="6" t="n">
         <v>0.231</v>
       </c>
-      <c r="L29" s="6" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="S29" s="6" t="n">
-        <v>0.241</v>
+      <c r="V29" s="6" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <v>0.302</v>
       </c>
     </row>
     <row r="30">
@@ -2098,59 +2236,67 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.047</v>
+        <v>0.053</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>0.044</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.189</v>
+        <v>0.259</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.147</v>
+        <v>0.183</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.09</v>
+        <v>0.092</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.336</v>
+        <v>0.252</v>
       </c>
       <c r="K30" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="P30" s="7" t="n"/>
+      <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="7" t="n"/>
+      <c r="S30" s="7" t="n"/>
+      <c r="T30" s="6" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="U30" s="6" t="n">
         <v>0.231</v>
       </c>
-      <c r="L30" s="6" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="S30" s="6" t="n">
-        <v>0.241</v>
+      <c r="V30" s="6" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="W30" s="6" t="n">
+        <v>0.302</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2159,52 +2305,56 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>0.098</v>
       </c>
-      <c r="E31" s="6" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>0.037</v>
-      </c>
       <c r="I31" s="6" t="n">
-        <v>0.029</v>
+        <v>0.076</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.543</v>
+        <v>0.355</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.438</v>
+        <v>0.309</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.125</v>
+        <v>0.059</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.15</v>
+        <v>0.054</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.422</v>
+        <v>0.388</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="P31" s="6" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="S31" s="6" t="n">
-        <v>0.278</v>
+      <c r="P31" s="7" t="n"/>
+      <c r="Q31" s="7" t="n"/>
+      <c r="R31" s="7" t="n"/>
+      <c r="S31" s="7" t="n"/>
+      <c r="T31" s="6" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="W31" s="6" t="n">
+        <v>0.241</v>
       </c>
     </row>
     <row r="32">
@@ -2216,52 +2366,56 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.098</v>
+        <v>0.047</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.115</v>
+        <v>0.044</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.303</v>
+        <v>0.189</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.16</v>
+        <v>0.147</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.039</v>
+        <v>0.11</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.491</v>
+        <v>0.336</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.319</v>
+        <v>0.231</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.126</v>
+        <v>0.062</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.153</v>
+        <v>0.057</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.423</v>
+        <v>0.396</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="S32" s="6" t="n">
-        <v>0.278</v>
+        <v>0.282</v>
+      </c>
+      <c r="P32" s="7" t="n"/>
+      <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="7" t="n"/>
+      <c r="S32" s="7" t="n"/>
+      <c r="T32" s="6" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="U32" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="W32" s="6" t="n">
+        <v>0.241</v>
       </c>
     </row>
     <row r="33">
@@ -2273,63 +2427,63 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.098</v>
+        <v>0.047</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.115</v>
+        <v>0.044</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.303</v>
+        <v>0.189</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.16</v>
+        <v>0.147</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.039</v>
+        <v>0.11</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.491</v>
+        <v>0.336</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.319</v>
+        <v>0.231</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.126</v>
+        <v>0.062</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.153</v>
+        <v>0.057</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.423</v>
+        <v>0.396</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="S33" s="6" t="n">
-        <v>0.278</v>
+        <v>0.282</v>
+      </c>
+      <c r="P33" s="7" t="n"/>
+      <c r="Q33" s="7" t="n"/>
+      <c r="R33" s="7" t="n"/>
+      <c r="S33" s="7" t="n"/>
+      <c r="T33" s="6" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="U33" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="W33" s="6" t="n">
+        <v>0.241</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
+      <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2338,52 +2492,56 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>0.036</v>
+        <v>0.098</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.038</v>
+        <v>0.115</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.113</v>
+        <v>0.304</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.039</v>
+        <v>0.029</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.628</v>
+        <v>0.543</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.303</v>
+        <v>0.438</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.052</v>
+        <v>0.125</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.294</v>
+        <v>0.422</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="S34" s="6" t="n">
-        <v>0.275</v>
+        <v>0.187</v>
+      </c>
+      <c r="P34" s="7" t="n"/>
+      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n"/>
+      <c r="S34" s="7" t="n"/>
+      <c r="T34" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U34" s="6" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="W34" s="6" t="n">
+        <v>0.278</v>
       </c>
     </row>
     <row r="35">
@@ -2395,52 +2553,56 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.036</v>
+        <v>0.098</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.038</v>
+        <v>0.115</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.112</v>
+        <v>0.303</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.058</v>
+        <v>0.039</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.066</v>
+        <v>0.03</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.491</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.161</v>
+        <v>0.319</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.053</v>
+        <v>0.126</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.052</v>
+        <v>0.153</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.293</v>
+        <v>0.423</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="S35" s="6" t="n">
-        <v>0.181</v>
+        <v>0.186</v>
+      </c>
+      <c r="P35" s="7" t="n"/>
+      <c r="Q35" s="7" t="n"/>
+      <c r="R35" s="7" t="n"/>
+      <c r="S35" s="7" t="n"/>
+      <c r="T35" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="W35" s="6" t="n">
+        <v>0.278</v>
       </c>
     </row>
     <row r="36">
@@ -2452,59 +2614,67 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.036</v>
+        <v>0.098</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.038</v>
+        <v>0.115</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.112</v>
+        <v>0.303</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.058</v>
+        <v>0.039</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.066</v>
+        <v>0.03</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.491</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.161</v>
+        <v>0.319</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.053</v>
+        <v>0.126</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.052</v>
+        <v>0.153</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.293</v>
+        <v>0.423</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="S36" s="6" t="n">
-        <v>0.181</v>
+        <v>0.186</v>
+      </c>
+      <c r="P36" s="7" t="n"/>
+      <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="7" t="n"/>
+      <c r="S36" s="7" t="n"/>
+      <c r="T36" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="W36" s="6" t="n">
+        <v>0.278</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2513,52 +2683,56 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.128</v>
+        <v>0.036</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.145</v>
+        <v>0.038</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.333</v>
+        <v>0.113</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.212</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H37" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="M37" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="L37" s="6" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="M37" s="6" t="n">
-        <v>0.233</v>
-      </c>
       <c r="N37" s="6" t="n">
-        <v>0.363</v>
+        <v>0.294</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="S37" s="6" t="n">
-        <v>0.269</v>
+        <v>0.17</v>
+      </c>
+      <c r="P37" s="7" t="n"/>
+      <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="7" t="n"/>
+      <c r="S37" s="7" t="n"/>
+      <c r="T37" s="6" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="U37" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V37" s="6" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="W37" s="6" t="n">
+        <v>0.275</v>
       </c>
     </row>
     <row r="38">
@@ -2570,52 +2744,56 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0.128</v>
+        <v>0.036</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.145</v>
+        <v>0.038</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.332</v>
+        <v>0.112</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.212</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.077</v>
+        <v>0.058</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.099</v>
+        <v>0.066</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.515</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K38" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="O38" s="6" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="P38" s="7" t="n"/>
+      <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="7" t="n"/>
+      <c r="S38" s="7" t="n"/>
+      <c r="T38" s="6" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="U38" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="V38" s="6" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="W38" s="6" t="n">
         <v>0.181</v>
-      </c>
-      <c r="L38" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="M38" s="6" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="N38" s="6" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="O38" s="6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="S38" s="6" t="n">
-        <v>0.234</v>
       </c>
     </row>
     <row r="39">
@@ -2627,63 +2805,63 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.128</v>
+        <v>0.036</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.145</v>
+        <v>0.038</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.332</v>
+        <v>0.112</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.212</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.077</v>
+        <v>0.058</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.099</v>
+        <v>0.066</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.515</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K39" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="P39" s="7" t="n"/>
+      <c r="Q39" s="7" t="n"/>
+      <c r="R39" s="7" t="n"/>
+      <c r="S39" s="7" t="n"/>
+      <c r="T39" s="6" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="W39" s="6" t="n">
         <v>0.181</v>
-      </c>
-      <c r="L39" s="6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="M39" s="6" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="N39" s="6" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="O39" s="6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="S39" s="6" t="n">
-        <v>0.234</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
+      <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2692,52 +2870,56 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.012</v>
+        <v>0.128</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.008</v>
+        <v>0.145</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.129</v>
+        <v>0.333</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.129</v>
+        <v>0.212</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.095</v>
+        <v>0.05</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.068</v>
+        <v>0.055</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.529</v>
+        <v>0.5</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.436</v>
+        <v>0.157</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.031</v>
+        <v>0.228</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.022</v>
+        <v>0.233</v>
       </c>
       <c r="N40" s="6" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="O40" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P40" s="7" t="n"/>
+      <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="7" t="n"/>
+      <c r="S40" s="7" t="n"/>
+      <c r="T40" s="6" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="U40" s="6" t="n">
         <v>0.309</v>
       </c>
-      <c r="O40" s="6" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v>0.28</v>
+      <c r="V40" s="6" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.269</v>
       </c>
     </row>
     <row r="41">
@@ -2749,52 +2931,56 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.012</v>
+        <v>0.128</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.008</v>
+        <v>0.145</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.129</v>
+        <v>0.332</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.129</v>
+        <v>0.212</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.128</v>
+        <v>0.077</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.111</v>
+        <v>0.099</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.467</v>
+        <v>0.515</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>0.319</v>
+        <v>0.181</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.031</v>
+        <v>0.231</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.022</v>
+        <v>0.238</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.309</v>
+        <v>0.351</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="S41" s="6" t="n">
-        <v>0.249</v>
+        <v>0.182</v>
+      </c>
+      <c r="P41" s="7" t="n"/>
+      <c r="Q41" s="7" t="n"/>
+      <c r="R41" s="7" t="n"/>
+      <c r="S41" s="7" t="n"/>
+      <c r="T41" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>0.234</v>
       </c>
     </row>
     <row r="42">
@@ -2806,64 +2992,261 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="P42" s="7" t="n"/>
+      <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="7" t="n"/>
+      <c r="S42" s="7" t="n"/>
+      <c r="T42" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="U42" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="V42" s="6" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="W42" s="6" t="n">
+        <v>0.234</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
         <v>0.012</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E43" s="6" t="n">
         <v>0.008</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F43" s="6" t="n">
         <v>0.129</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G43" s="6" t="n">
         <v>0.129</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H43" s="6" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P43" s="7" t="n"/>
+      <c r="Q43" s="7" t="n"/>
+      <c r="R43" s="7" t="n"/>
+      <c r="S43" s="7" t="n"/>
+      <c r="T43" s="6" t="n">
         <v>0.128</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="U43" s="6" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="V43" s="6" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="W43" s="6" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I44" s="6" t="n">
         <v>0.111</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J44" s="6" t="n">
         <v>0.467</v>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="K44" s="6" t="n">
         <v>0.319</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L44" s="6" t="n">
         <v>0.031</v>
       </c>
-      <c r="M42" s="6" t="n">
+      <c r="M44" s="6" t="n">
         <v>0.022</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="N44" s="6" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P44" s="7" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="7" t="n"/>
+      <c r="S44" s="7" t="n"/>
+      <c r="T44" s="6" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="U44" s="6" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="W44" s="6" t="n">
+        <v>0.249</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N45" s="6" t="n">
         <v>0.304</v>
       </c>
-      <c r="O42" s="6" t="n">
+      <c r="O45" s="6" t="n">
         <v>0.241</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="P45" s="7" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="7" t="n"/>
+      <c r="S45" s="7" t="n"/>
+      <c r="T45" s="6" t="n">
         <v>0.142</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="U45" s="6" t="n">
         <v>0.189</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="V45" s="6" t="n">
         <v>0.505</v>
       </c>
-      <c r="S42" s="6" t="n">
+      <c r="W45" s="6" t="n">
         <v>0.249</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
+    <mergeCell ref="T2:W2"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="L1:O1"/>
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="P2:S2"/>
+    <mergeCell ref="T1:W1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D9">
     <cfRule type="colorScale" priority="1">
@@ -3057,8 +3440,56 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="T4:T9">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U4:U9">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V4:V9">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W4:W9">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D10:D15">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3070,7 +3501,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E15">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3082,7 +3513,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F15">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3094,7 +3525,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G15">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3106,7 +3537,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H15">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3118,7 +3549,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:I15">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3130,7 +3561,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J10:J15">
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3142,7 +3573,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K10:K15">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3154,7 +3585,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:L15">
-    <cfRule type="colorScale" priority="25">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3166,7 +3597,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:M15">
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3178,7 +3609,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:N15">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3190,7 +3621,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10:O15">
-    <cfRule type="colorScale" priority="28">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3202,7 +3633,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P15">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3214,7 +3645,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q10:Q15">
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3226,7 +3657,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R15">
-    <cfRule type="colorScale" priority="31">
+    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3238,7 +3669,55 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S15">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T10:T15">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U10:U15">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V10:V15">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W10:W15">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3250,7 +3729,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D18">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3262,7 +3741,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16:E18">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3274,7 +3753,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F18">
-    <cfRule type="colorScale" priority="35">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3286,7 +3765,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16:G18">
-    <cfRule type="colorScale" priority="36">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3298,7 +3777,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H18">
-    <cfRule type="colorScale" priority="37">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3310,7 +3789,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I18">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3322,7 +3801,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16:J18">
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3334,7 +3813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:K18">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3346,7 +3825,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16:L18">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3358,7 +3837,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16:M18">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3370,7 +3849,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16:N18">
-    <cfRule type="colorScale" priority="43">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3382,7 +3861,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O16:O18">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3394,7 +3873,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P16:P18">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3406,7 +3885,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:Q18">
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3418,7 +3897,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R16:R18">
-    <cfRule type="colorScale" priority="47">
+    <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3430,7 +3909,55 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S16:S18">
-    <cfRule type="colorScale" priority="48">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T16:T18">
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U16:U18">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V16:V18">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W16:W18">
+    <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3442,7 +3969,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D21">
-    <cfRule type="colorScale" priority="49">
+    <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3454,7 +3981,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E21">
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3466,7 +3993,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F21">
-    <cfRule type="colorScale" priority="51">
+    <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3478,7 +4005,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G21">
-    <cfRule type="colorScale" priority="52">
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3490,7 +4017,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:H21">
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3502,7 +4029,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I21">
-    <cfRule type="colorScale" priority="54">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3514,7 +4041,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19:J21">
-    <cfRule type="colorScale" priority="55">
+    <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3526,7 +4053,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:K21">
-    <cfRule type="colorScale" priority="56">
+    <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3538,7 +4065,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L19:L21">
-    <cfRule type="colorScale" priority="57">
+    <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3550,7 +4077,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:M21">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3562,7 +4089,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:N21">
-    <cfRule type="colorScale" priority="59">
+    <cfRule type="colorScale" priority="71">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3574,7 +4101,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O21">
-    <cfRule type="colorScale" priority="60">
+    <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3586,7 +4113,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P21">
-    <cfRule type="colorScale" priority="61">
+    <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3598,7 +4125,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q19:Q21">
-    <cfRule type="colorScale" priority="62">
+    <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3610,7 +4137,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19:R21">
-    <cfRule type="colorScale" priority="63">
+    <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3622,150 +4149,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:S21">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22:D27">
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22:E27">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22:F27">
-    <cfRule type="colorScale" priority="67">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G27">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:H27">
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I27">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J22:J27">
-    <cfRule type="colorScale" priority="71">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K22:K27">
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L22:L27">
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M22:M27">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22:N27">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8D7DA"/>
-        <color rgb="00FFF3CD"/>
-        <color rgb="00D4EDDA"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O22:O27">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -3777,7 +4160,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P22:P27">
+  <conditionalFormatting sqref="T19:T21">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -3789,7 +4172,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q22:Q27">
+  <conditionalFormatting sqref="U19:U21">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="min"/>
@@ -3801,7 +4184,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R22:R27">
+  <conditionalFormatting sqref="V19:V21">
     <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
@@ -3813,7 +4196,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S22:S27">
+  <conditionalFormatting sqref="W19:W21">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -3825,7 +4208,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D28:D33">
+  <conditionalFormatting sqref="D22:D24">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -3837,7 +4220,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28:E33">
+  <conditionalFormatting sqref="E22:E24">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -3849,7 +4232,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F33">
+  <conditionalFormatting sqref="F22:F24">
     <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
@@ -3861,7 +4244,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:G33">
+  <conditionalFormatting sqref="G22:G24">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -3873,7 +4256,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28:H33">
+  <conditionalFormatting sqref="H22:H24">
     <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="min"/>
@@ -3885,7 +4268,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I28:I33">
+  <conditionalFormatting sqref="I22:I24">
     <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min"/>
@@ -3897,7 +4280,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28:J33">
+  <conditionalFormatting sqref="J22:J24">
     <cfRule type="colorScale" priority="87">
       <colorScale>
         <cfvo type="min"/>
@@ -3909,7 +4292,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K28:K33">
+  <conditionalFormatting sqref="K22:K24">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min"/>
@@ -3921,7 +4304,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L28:L33">
+  <conditionalFormatting sqref="L22:L24">
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -3933,7 +4316,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M28:M33">
+  <conditionalFormatting sqref="M22:M24">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
@@ -3945,7 +4328,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N28:N33">
+  <conditionalFormatting sqref="N22:N24">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -3957,7 +4340,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O28:O33">
+  <conditionalFormatting sqref="O22:O24">
     <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="min"/>
@@ -3969,7 +4352,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P28:P33">
+  <conditionalFormatting sqref="P22:P24">
     <cfRule type="colorScale" priority="93">
       <colorScale>
         <cfvo type="min"/>
@@ -3981,7 +4364,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q28:Q33">
+  <conditionalFormatting sqref="Q22:Q24">
     <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="min"/>
@@ -3993,7 +4376,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R28:R33">
+  <conditionalFormatting sqref="R22:R24">
     <cfRule type="colorScale" priority="95">
       <colorScale>
         <cfvo type="min"/>
@@ -4005,7 +4388,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S28:S33">
+  <conditionalFormatting sqref="S22:S24">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
@@ -4017,7 +4400,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D34:D39">
+  <conditionalFormatting sqref="T22:T24">
     <cfRule type="colorScale" priority="97">
       <colorScale>
         <cfvo type="min"/>
@@ -4029,7 +4412,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34:E39">
+  <conditionalFormatting sqref="U22:U24">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -4041,7 +4424,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34:F39">
+  <conditionalFormatting sqref="V22:V24">
     <cfRule type="colorScale" priority="99">
       <colorScale>
         <cfvo type="min"/>
@@ -4053,7 +4436,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G39">
+  <conditionalFormatting sqref="W22:W24">
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min"/>
@@ -4065,7 +4448,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H39">
+  <conditionalFormatting sqref="D25:D30">
     <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
@@ -4077,7 +4460,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I34:I39">
+  <conditionalFormatting sqref="E25:E30">
     <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min"/>
@@ -4089,7 +4472,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J39">
+  <conditionalFormatting sqref="F25:F30">
     <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
@@ -4101,7 +4484,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K34:K39">
+  <conditionalFormatting sqref="G25:G30">
     <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
@@ -4113,7 +4496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L34:L39">
+  <conditionalFormatting sqref="H25:H30">
     <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
@@ -4125,7 +4508,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34:M39">
+  <conditionalFormatting sqref="I25:I30">
     <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
@@ -4137,7 +4520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N34:N39">
+  <conditionalFormatting sqref="J25:J30">
     <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
@@ -4149,7 +4532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O34:O39">
+  <conditionalFormatting sqref="K25:K30">
     <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min"/>
@@ -4161,7 +4544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P34:P39">
+  <conditionalFormatting sqref="L25:L30">
     <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
@@ -4173,7 +4556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q34:Q39">
+  <conditionalFormatting sqref="M25:M30">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="min"/>
@@ -4185,7 +4568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R34:R39">
+  <conditionalFormatting sqref="N25:N30">
     <cfRule type="colorScale" priority="111">
       <colorScale>
         <cfvo type="min"/>
@@ -4197,7 +4580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S34:S39">
+  <conditionalFormatting sqref="O25:O30">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="min"/>
@@ -4209,7 +4592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D40:D42">
+  <conditionalFormatting sqref="P25:P30">
     <cfRule type="colorScale" priority="113">
       <colorScale>
         <cfvo type="min"/>
@@ -4221,7 +4604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E40:E42">
+  <conditionalFormatting sqref="Q25:Q30">
     <cfRule type="colorScale" priority="114">
       <colorScale>
         <cfvo type="min"/>
@@ -4233,7 +4616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F40:F42">
+  <conditionalFormatting sqref="R25:R30">
     <cfRule type="colorScale" priority="115">
       <colorScale>
         <cfvo type="min"/>
@@ -4245,7 +4628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G40:G42">
+  <conditionalFormatting sqref="S25:S30">
     <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="min"/>
@@ -4257,7 +4640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H40:H42">
+  <conditionalFormatting sqref="T25:T30">
     <cfRule type="colorScale" priority="117">
       <colorScale>
         <cfvo type="min"/>
@@ -4269,7 +4652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I40:I42">
+  <conditionalFormatting sqref="U25:U30">
     <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min"/>
@@ -4281,7 +4664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J40:J42">
+  <conditionalFormatting sqref="V25:V30">
     <cfRule type="colorScale" priority="119">
       <colorScale>
         <cfvo type="min"/>
@@ -4293,7 +4676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K40:K42">
+  <conditionalFormatting sqref="W25:W30">
     <cfRule type="colorScale" priority="120">
       <colorScale>
         <cfvo type="min"/>
@@ -4305,7 +4688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L40:L42">
+  <conditionalFormatting sqref="D31:D36">
     <cfRule type="colorScale" priority="121">
       <colorScale>
         <cfvo type="min"/>
@@ -4317,7 +4700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M40:M42">
+  <conditionalFormatting sqref="E31:E36">
     <cfRule type="colorScale" priority="122">
       <colorScale>
         <cfvo type="min"/>
@@ -4329,7 +4712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N40:N42">
+  <conditionalFormatting sqref="F31:F36">
     <cfRule type="colorScale" priority="123">
       <colorScale>
         <cfvo type="min"/>
@@ -4341,7 +4724,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O40:O42">
+  <conditionalFormatting sqref="G31:G36">
     <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="min"/>
@@ -4353,7 +4736,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P40:P42">
+  <conditionalFormatting sqref="H31:H36">
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -4365,7 +4748,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q40:Q42">
+  <conditionalFormatting sqref="I31:I36">
     <cfRule type="colorScale" priority="126">
       <colorScale>
         <cfvo type="min"/>
@@ -4377,7 +4760,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R40:R42">
+  <conditionalFormatting sqref="J31:J36">
     <cfRule type="colorScale" priority="127">
       <colorScale>
         <cfvo type="min"/>
@@ -4389,8 +4772,632 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S40:S42">
+  <conditionalFormatting sqref="K31:K36">
     <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L31:L36">
+    <cfRule type="colorScale" priority="129">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M31:M36">
+    <cfRule type="colorScale" priority="130">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N31:N36">
+    <cfRule type="colorScale" priority="131">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O31:O36">
+    <cfRule type="colorScale" priority="132">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P31:P36">
+    <cfRule type="colorScale" priority="133">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q31:Q36">
+    <cfRule type="colorScale" priority="134">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R31:R36">
+    <cfRule type="colorScale" priority="135">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S31:S36">
+    <cfRule type="colorScale" priority="136">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T31:T36">
+    <cfRule type="colorScale" priority="137">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U31:U36">
+    <cfRule type="colorScale" priority="138">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V31:V36">
+    <cfRule type="colorScale" priority="139">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W31:W36">
+    <cfRule type="colorScale" priority="140">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37:D42">
+    <cfRule type="colorScale" priority="141">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:E42">
+    <cfRule type="colorScale" priority="142">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37:F42">
+    <cfRule type="colorScale" priority="143">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37:G42">
+    <cfRule type="colorScale" priority="144">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37:H42">
+    <cfRule type="colorScale" priority="145">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I37:I42">
+    <cfRule type="colorScale" priority="146">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37:J42">
+    <cfRule type="colorScale" priority="147">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:K42">
+    <cfRule type="colorScale" priority="148">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L37:L42">
+    <cfRule type="colorScale" priority="149">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M37:M42">
+    <cfRule type="colorScale" priority="150">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N37:N42">
+    <cfRule type="colorScale" priority="151">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O37:O42">
+    <cfRule type="colorScale" priority="152">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P37:P42">
+    <cfRule type="colorScale" priority="153">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q37:Q42">
+    <cfRule type="colorScale" priority="154">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R37:R42">
+    <cfRule type="colorScale" priority="155">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S37:S42">
+    <cfRule type="colorScale" priority="156">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T37:T42">
+    <cfRule type="colorScale" priority="157">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U37:U42">
+    <cfRule type="colorScale" priority="158">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V37:V42">
+    <cfRule type="colorScale" priority="159">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W37:W42">
+    <cfRule type="colorScale" priority="160">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D43:D45">
+    <cfRule type="colorScale" priority="161">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E43:E45">
+    <cfRule type="colorScale" priority="162">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43:F45">
+    <cfRule type="colorScale" priority="163">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43:G45">
+    <cfRule type="colorScale" priority="164">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H43:H45">
+    <cfRule type="colorScale" priority="165">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I43:I45">
+    <cfRule type="colorScale" priority="166">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J43:J45">
+    <cfRule type="colorScale" priority="167">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K43:K45">
+    <cfRule type="colorScale" priority="168">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L43:L45">
+    <cfRule type="colorScale" priority="169">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M43:M45">
+    <cfRule type="colorScale" priority="170">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N43:N45">
+    <cfRule type="colorScale" priority="171">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O43:O45">
+    <cfRule type="colorScale" priority="172">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P43:P45">
+    <cfRule type="colorScale" priority="173">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q43:Q45">
+    <cfRule type="colorScale" priority="174">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R43:R45">
+    <cfRule type="colorScale" priority="175">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S43:S45">
+    <cfRule type="colorScale" priority="176">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T43:T45">
+    <cfRule type="colorScale" priority="177">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U43:U45">
+    <cfRule type="colorScale" priority="178">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V43:V45">
+    <cfRule type="colorScale" priority="179">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W43:W45">
+    <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -1477,10 +1477,18 @@
       <c r="O16" s="6" t="n">
         <v>0.197</v>
       </c>
-      <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="7" t="n"/>
-      <c r="R16" s="7" t="n"/>
-      <c r="S16" s="7" t="n"/>
+      <c r="P16" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>0.303</v>
+      </c>
       <c r="T16" s="7" t="n"/>
       <c r="U16" s="7" t="n"/>
       <c r="V16" s="7" t="n"/>
@@ -1522,10 +1530,18 @@
       <c r="O17" s="6" t="n">
         <v>0.189</v>
       </c>
-      <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="7" t="n"/>
-      <c r="R17" s="7" t="n"/>
-      <c r="S17" s="7" t="n"/>
+      <c r="P17" s="6" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0.284</v>
+      </c>
       <c r="T17" s="7" t="n"/>
       <c r="U17" s="7" t="n"/>
       <c r="V17" s="7" t="n"/>
@@ -1567,10 +1583,18 @@
       <c r="O18" s="6" t="n">
         <v>0.189</v>
       </c>
-      <c r="P18" s="7" t="n"/>
-      <c r="Q18" s="7" t="n"/>
-      <c r="R18" s="7" t="n"/>
-      <c r="S18" s="7" t="n"/>
+      <c r="P18" s="6" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>0.284</v>
+      </c>
       <c r="T18" s="7" t="n"/>
       <c r="U18" s="7" t="n"/>
       <c r="V18" s="7" t="n"/>

--- a/results/eval_outputs/master_comparison.xlsx
+++ b/results/eval_outputs/master_comparison.xlsx
@@ -1461,10 +1461,18 @@
       <c r="G16" s="6" t="n">
         <v>0.242</v>
       </c>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
+      <c r="H16" s="6" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0.241</v>
+      </c>
       <c r="L16" s="6" t="n">
         <v>0.147</v>
       </c>
@@ -1489,10 +1497,18 @@
       <c r="S16" s="6" t="n">
         <v>0.303</v>
       </c>
-      <c r="T16" s="7" t="n"/>
-      <c r="U16" s="7" t="n"/>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="n"/>
+      <c r="T16" s="6" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="U16" s="6" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="V16" s="6" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="W16" s="6" t="n">
+        <v>0.317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1514,10 +1530,18 @@
       <c r="G17" s="6" t="n">
         <v>0.242</v>
       </c>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
+      <c r="H17" s="6" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0.196</v>
+      </c>
       <c r="L17" s="6" t="n">
         <v>0.15</v>
       </c>
@@ -1542,10 +1566,18 @@
       <c r="S17" s="6" t="n">
         <v>0.284</v>
       </c>
-      <c r="T17" s="7" t="n"/>
-      <c r="U17" s="7" t="n"/>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="7" t="n"/>
+      <c r="T17" s="6" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0.314</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1567,10 +1599,18 @@
       <c r="G18" s="6" t="n">
         <v>0.242</v>
       </c>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0.196</v>
+      </c>
       <c r="L18" s="6" t="n">
         <v>0.15</v>
       </c>
@@ -1595,10 +1635,18 @@
       <c r="S18" s="6" t="n">
         <v>0.284</v>
       </c>
-      <c r="T18" s="7" t="n"/>
-      <c r="U18" s="7" t="n"/>
-      <c r="V18" s="7" t="n"/>
-      <c r="W18" s="7" t="n"/>
+      <c r="T18" s="6" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="V18" s="6" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="W18" s="6" t="n">
+        <v>0.314</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1628,10 +1676,18 @@
       <c r="G19" s="6" t="n">
         <v>0.189</v>
       </c>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
+      <c r="H19" s="6" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0.187</v>
+      </c>
       <c r="L19" s="6" t="n">
         <v>0.135</v>
       </c>
@@ -1656,10 +1712,18 @@
       <c r="S19" s="6" t="n">
         <v>0.335</v>
       </c>
-      <c r="T19" s="7" t="n"/>
-      <c r="U19" s="7" t="n"/>
-      <c r="V19" s="7" t="n"/>
-      <c r="W19" s="7" t="n"/>
+      <c r="T19" s="6" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0.306</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1681,10 +1745,18 @@
       <c r="G20" s="6" t="n">
         <v>0.191</v>
       </c>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
+      <c r="H20" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0.17</v>
+      </c>
       <c r="L20" s="6" t="n">
         <v>0.135</v>
       </c>
@@ -1709,10 +1781,18 @@
       <c r="S20" s="6" t="n">
         <v>0.245</v>
       </c>
-      <c r="T20" s="7" t="n"/>
-      <c r="U20" s="7" t="n"/>
-      <c r="V20" s="7" t="n"/>
-      <c r="W20" s="7" t="n"/>
+      <c r="T20" s="6" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0.299</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1734,10 +1814,18 @@
       <c r="G21" s="6" t="n">
         <v>0.191</v>
       </c>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
+      <c r="H21" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.17</v>
+      </c>
       <c r="L21" s="6" t="n">
         <v>0.135</v>
       </c>
@@ -1762,10 +1850,18 @@
       <c r="S21" s="6" t="n">
         <v>0.245</v>
       </c>
-      <c r="T21" s="7" t="n"/>
-      <c r="U21" s="7" t="n"/>
-      <c r="V21" s="7" t="n"/>
-      <c r="W21" s="7" t="n"/>
+      <c r="T21" s="6" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.299</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1795,10 +1891,18 @@
       <c r="G22" s="6" t="n">
         <v>0.228</v>
       </c>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
+      <c r="H22" s="6" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0.133</v>
+      </c>
       <c r="L22" s="6" t="n">
         <v>0.191</v>
       </c>
@@ -1823,10 +1927,18 @@
       <c r="S22" s="6" t="n">
         <v>0.335</v>
       </c>
-      <c r="T22" s="7" t="n"/>
-      <c r="U22" s="7" t="n"/>
-      <c r="V22" s="7" t="n"/>
-      <c r="W22" s="7" t="n"/>
+      <c r="T22" s="6" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="U22" s="6" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="W22" s="6" t="n">
+        <v>0.277</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1848,10 +1960,18 @@
       <c r="G23" s="6" t="n">
         <v>0.226</v>
       </c>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
+      <c r="H23" s="6" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0.126</v>
+      </c>
       <c r="L23" s="6" t="n">
         <v>0.194</v>
       </c>
@@ -1876,10 +1996,18 @@
       <c r="S23" s="6" t="n">
         <v>0.324</v>
       </c>
-      <c r="T23" s="7" t="n"/>
-      <c r="U23" s="7" t="n"/>
-      <c r="V23" s="7" t="n"/>
-      <c r="W23" s="7" t="n"/>
+      <c r="T23" s="6" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>0.278</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1901,10 +2029,18 @@
       <c r="G24" s="6" t="n">
         <v>0.226</v>
       </c>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
+      <c r="H24" s="6" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0.126</v>
+      </c>
       <c r="L24" s="6" t="n">
         <v>0.194</v>
       </c>
@@ -1929,10 +2065,18 @@
       <c r="S24" s="6" t="n">
         <v>0.324</v>
       </c>
-      <c r="T24" s="7" t="n"/>
-      <c r="U24" s="7" t="n"/>
-      <c r="V24" s="7" t="n"/>
-      <c r="W24" s="7" t="n"/>
+      <c r="T24" s="6" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <v>0.278</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
